--- a/dataset/全国重点院校/全国高校汇总表.xlsx
+++ b/dataset/全国重点院校/全国高校汇总表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3972" uniqueCount="1561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3972" uniqueCount="1571">
   <si>
     <t>全国高校汇总表（软科中国top150目标 · 共 188 所 · 含就业/研究生/国际处渠道与理工学院）</t>
   </si>
@@ -2869,6 +2869,10 @@
     <t>ied@ybu.edu.cn</t>
   </si>
   <si>
+    <t>理学院 | https://science.ybu.edu.cn/ | 邮箱:lxy@ybu.edu.cn; piaohs@ybu.edu.cn; lyjin@ybu.edu.cn | 电话:(0433)-2732242
+地理与海洋科学学院 | https://cgos.ybu.edu.cn | 邮箱:dhxy@ybu.edu.cn | 电话:0433-8175105; 0433-8175117; 0433-8175119</t>
+  </si>
+  <si>
     <t>四川农业大学</t>
   </si>
   <si>
@@ -4254,6 +4258,17 @@
     <t>danyangliu@dlmu.edu.cn; nanli@dlmu.edu.cn; amberwu@dlmu.edu.cn</t>
   </si>
   <si>
+    <t>轮机工程学院 | http://mec.dlmu.edu.cn/
+船舶电气工程学院 | http://cbdq.dlmu.edu.cn/ | 电话:0411-84727620
+信息科学技术学院 | http://ist.dlmu.edu.cn/
+交通运输工程学院 | http://jt.dlmu.edu.cn/
+船舶与海洋工程学院 | http://teoec.dlmu.edu.cn/ | 电话:0411-84723959
+环境科学与工程学院 | http://huangong.dlmu.edu.cn/ | 电话:19196649850
+人工智能学院 | http://ai.dlmu.edu.cn/ | 邮箱:ai-undergraduate@dlmu.edu.cn; ai-postgraduate@dlmu.edu.cn; ai-faculty@dlmu.edu.cn | 电话:0411-84724558
+理学院 | http://science.dlmu.edu.cn/ | 电话:0411-84729332; 0411-84723683; 0411-84729204
+卓越工程师学院 | https://gcee.dlmu.edu.cn/</t>
+  </si>
+  <si>
     <t>辽宁大学</t>
   </si>
   <si>
@@ -4278,6 +4293,13 @@
     <t>曲艺 副处长
 谢名一 处长
 尹如玉 副处长</t>
+  </si>
+  <si>
+    <t>数学与统计学院 | http://ms.lnu.edu.cn/ | 邮箱:lnuxyh@126.com; 176938645@qq.com | 电话:024-62202209
+物理学院 | http://phys.lnu.edu.cn/ | 电话:024-62202306
+化学院 | http://chem.lnu.edu.cn/ | 邮箱:hgxy@lnu.edu.cn | 电话:024-62202380; 024-62202053; 024-62205208
+生命科学院 | http://lifesci.lnu.edu.cn/ | 电话:024-62202232
+环境学院 | http://envi.lnu.edu.cn/ | 电话:024-62204818</t>
   </si>
   <si>
     <t>西南大学</t>
@@ -4587,6 +4609,19 @@
 迟勇及 副处长（负责人热情接待了代表团一行）</t>
   </si>
   <si>
+    <t>科学技术研究院 | https://kxjsc.neau.edu.cn/
+资源与环境学院 | http://zhxy.neau.edu.cn/
+农业装备与能源工程学院 | https://gcxy.neau.edu.cn/ | 邮箱:gongchengjiwei@neau.edu.cn | 电话:0451-55190667
+水利科学与工程学院 | http://slxy.neau.edu.cn/
+动物科学技术学院 | http://dwkxjsxy.neau.edu.cn/
+生命科学学院 | http://smkxxy.neau.edu.cn/
+食品学院 | http://spxy.neau.edu.cn/
+化学与分子工程学院 | http://wlxy.neau.edu.cn/
+智能科学与工程学院 | http://dqxx.neau.edu.cn/
+黑龙江省绿色食品科学研究院 | http://www.hgfsri.org.cn/ | 邮箱:hljlssky@163.com | 电话:0451-87199077
+计算机基础教学部</t>
+  </si>
+  <si>
     <t>东北林业大学</t>
   </si>
   <si>
@@ -4618,6 +4653,18 @@
 孙治平 处长
 计晓艳 副处长: nefu_gjhzc@163.com
 的选聘 助理（负责学生助理的选聘、考核和日常管理工作；）</t>
+  </si>
+  <si>
+    <t>材料科学与工程学院 | https://cailiao.nefu.edu.cn/
+机电工程学院 | https://cmee.nefu.edu.cn/ | 电话:0451-82190397
+生命科学学院 | https://life.nefu.edu.cn/ | 邮箱:lyhshen@126.com; xuezhy@126.com
+土木与交通学院 | https://civil.nefu.edu.cn/
+计算机与人工智能学院 | https://scsai.nefu.edu.cn/ | 邮箱:ccec_jw@163.com | 电话:0451-82190421
+理学院 | https://science.nefu.edu.cn/
+化学化工与资源利用学院 | https://hzxy.nefu.edu.cn/
+未来技术学院 | https://future.nefu.edu.cn/ | 电话:0451-82192586（
+控制与信息工程学院 | https://ccie.nefu.edu.cn/ | 电话:0451-82191298
+食品与健康学院 | https://www.nefu.edu.cn/spyjkxy/</t>
   </si>
   <si>
     <t>哈尔滨工程大学</t>
@@ -5224,6 +5271,19 @@
 肖豫涵 副处长（负责涉外项目管理）</t>
   </si>
   <si>
+    <t>动物科学学院 | https://dongke.scau.edu.cn/ | 邮箱:dongkeoffice@scau.edu.cn | 电话:020-85280547; 020-85280740; 020-85280275
+资源环境学院 | https://zyhjxy.scau.edu.cn/ | 邮箱:zyhjxy@scau.edu.cn
+海洋学院 | https://hy.scau.edu.cn/ | 邮箱:hyxy@scau.edu.cn | 电话:020-85289907
+生命科学学院 | https://life.scau.edu.cn/ | 电话:020-85282180; 020-85280185
+工程学院 | https://gcxy.scau.edu.cn/ | 邮箱:gcjsxy@scau.edu.cn | 电话:020-85280783
+食品学院 | https://spxy.scau.edu.cn/ | 电话:020-85280266; 020-85280265; 020-85288295
+水利与土木工程学院 | https://wcce.scau.edu.cn/ | 邮箱:sltmxy@scau.edu.cn | 电话:020-85283606; 020-85283650; 020-85282190
+数学与信息学院、软件学院 | https://info.scau.edu.cn/ | 邮箱:2376472251@qq.com | 电话:020-85285383; 020-85283315; 020-85285393（
+人工智能与低空技术学院 | https://dzxy.scau.edu.cn/ | 电话:020-85283400; 020-85283522; 020-85285066
+材料与化学工程学院 | https://cmce.scau.edu.cn/
+广州都柏林国际生命科学与技术学院 | https://gdic.scau.edu.cn/ | 邮箱:gdic@scau.edu.cn | 电话:01060500010; 020-85283419--; 020-85280035</t>
+  </si>
+  <si>
     <t>南方科技大学</t>
   </si>
   <si>
@@ -5286,6 +5346,9 @@
     <t>https://www.gzucm.edu.cn/jyjx/gjjyjgatqxspy.htm</t>
   </si>
   <si>
+    <t>医学信息工程学院 | https://ygxy.gzucm.edu.cn</t>
+  </si>
+  <si>
     <t>广州医科大学</t>
   </si>
   <si>
@@ -5299,6 +5362,10 @@
   </si>
   <si>
     <t>https://fao.gzhmu.edu.cn/</t>
+  </si>
+  <si>
+    <t>生物医学工程学院 | https://bme.gzhmu.edu.cn/ | 邮箱:admin@www.cufe.edu.com | 电话:0326004485; 010-12345678
+儿科学院 | https://www.gzfezx.com/ | 邮箱:fezxllb@163.com | 电话:022030411271; 022030411280; 022030411535</t>
   </si>
   <si>
     <t>南京中医药大学</t>
@@ -5719,6 +5786,19 @@
     <t>http://www.cust.edu.cn/jlhz2026/gjhz20261/index.htm</t>
   </si>
   <si>
+    <t>科学技术研究院 | http://www.cust.edu.cn/kxyj2026/kxjsyjy2026/index.htm | 邮箱:cust@cust.edu.cn
+物理学院 | http://wlxy.cust.edu.cn/ | 电话:0431-85582524
+光电工程学院 | http://gd.cust.edu.cn/ | 邮箱:gdgc@cust.edu.cn | 电话:0431-85582246（; 0431-85582874（; 0431-85582875（
+机电工程学院 | http://me.cust.edu.cn/ | 邮箱:JDGCXY@cust.edu.cn | 电话:0431-85582259
+电子信息工程学院 | http://dx.cust.edu.cn/
+计算机科学技术学院 | http://cs.cust.edu.cn/
+人工智能学院、人工智能研究院 | http://ai.cust.edu.cn | 邮箱:ai@cust.edu.cn | 电话:0431-8558-3908
+材料科学与工程学院 | http://clkx.cust.edu.cn/ | 邮箱:wyc@cust.edu.cn | 电话:0431-85583188
+化学与环境工程学院 | http://hxhj.cust.edu.cn/
+数学与统计学院 | https://sxytjxy.cust.edu.cn/ | 邮箱:sxytjbg@cust.edu.cn | 电话:0431-85583266
+生命科学技术学院 | http://sls.cust.edu.cn/</t>
+  </si>
+  <si>
     <t>安徽农业大学</t>
   </si>
   <si>
@@ -6093,6 +6173,9 @@
   </si>
   <si>
     <t>http://wsc.gzhu.edu.cn/</t>
+  </si>
+  <si>
+    <t>科学研究院 | http://kyc.gzhu.edu.cn/ | 电话:39366239</t>
   </si>
   <si>
     <t>深圳大学</t>
@@ -12410,10 +12493,10 @@
         <v>26</v>
       </c>
       <c r="U69" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V69" s="4" t="s">
-        <v>26</v>
+        <v>590</v>
       </c>
       <c r="W69" s="4" t="s">
         <v>26</v>
@@ -12427,7 +12510,7 @@
         <v>139</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>26</v>
@@ -12439,22 +12522,22 @@
         <v>28</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M70" s="4" t="s">
         <v>26</v>
@@ -12466,7 +12549,7 @@
         <v>26</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="Q70" s="4" t="s">
         <v>26</v>
@@ -12484,7 +12567,7 @@
         <v>10</v>
       </c>
       <c r="V70" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="W70" s="4" t="s">
         <v>26</v>
@@ -12498,7 +12581,7 @@
         <v>139</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>26</v>
@@ -12510,22 +12593,22 @@
         <v>28</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M71" s="4" t="s">
         <v>26</v>
@@ -12534,10 +12617,10 @@
         <v>26</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q71" s="4" t="s">
         <v>26</v>
@@ -12546,7 +12629,7 @@
         <v>26</v>
       </c>
       <c r="S71" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="T71" s="4" t="s">
         <v>26</v>
@@ -12555,7 +12638,7 @@
         <v>20</v>
       </c>
       <c r="V71" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="W71" s="4" t="s">
         <v>26</v>
@@ -12569,7 +12652,7 @@
         <v>139</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>26</v>
@@ -12584,40 +12667,40 @@
         <v>26</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M72" s="4" t="s">
         <v>26</v>
       </c>
       <c r="N72" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="Q72" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R72" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="S72" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="T72" s="4" t="s">
         <v>26</v>
@@ -12626,7 +12709,7 @@
         <v>4</v>
       </c>
       <c r="V72" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="W72" s="4" t="s">
         <v>26</v>
@@ -12640,7 +12723,7 @@
         <v>154</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>26</v>
@@ -12679,7 +12762,7 @@
         <v>26</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="Q73" s="4" t="s">
         <v>26</v>
@@ -12708,10 +12791,10 @@
         <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>26</v>
@@ -12723,10 +12806,10 @@
         <v>28</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>26</v>
@@ -12735,10 +12818,10 @@
         <v>26</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M74" s="4" t="s">
         <v>26</v>
@@ -12750,7 +12833,7 @@
         <v>26</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="Q74" s="4" t="s">
         <v>26</v>
@@ -12759,7 +12842,7 @@
         <v>26</v>
       </c>
       <c r="S74" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="T74" s="4" t="s">
         <v>26</v>
@@ -12768,7 +12851,7 @@
         <v>19</v>
       </c>
       <c r="V74" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="W74" s="4" t="s">
         <v>26</v>
@@ -12782,7 +12865,7 @@
         <v>171</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>26</v>
@@ -12794,22 +12877,22 @@
         <v>28</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>26</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M75" s="4" t="s">
         <v>26</v>
@@ -12821,7 +12904,7 @@
         <v>26</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="Q75" s="4" t="s">
         <v>26</v>
@@ -12830,7 +12913,7 @@
         <v>26</v>
       </c>
       <c r="S75" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="T75" s="4" t="s">
         <v>26</v>
@@ -12839,7 +12922,7 @@
         <v>19</v>
       </c>
       <c r="V75" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="W75" s="4" t="s">
         <v>26</v>
@@ -12853,7 +12936,7 @@
         <v>171</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>26</v>
@@ -12865,7 +12948,7 @@
         <v>28</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H76" s="4" t="s">
         <v>26</v>
@@ -12892,7 +12975,7 @@
         <v>26</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="Q76" s="4" t="s">
         <v>26</v>
@@ -12910,7 +12993,7 @@
         <v>10</v>
       </c>
       <c r="V76" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="W76" s="4" t="s">
         <v>26</v>
@@ -12924,7 +13007,7 @@
         <v>182</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>26</v>
@@ -12936,10 +13019,10 @@
         <v>28</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>26</v>
@@ -12951,7 +13034,7 @@
         <v>26</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M77" s="4" t="s">
         <v>26</v>
@@ -12960,19 +13043,19 @@
         <v>26</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Q77" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R77" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="S77" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="T77" s="4" t="s">
         <v>26</v>
@@ -12981,7 +13064,7 @@
         <v>14</v>
       </c>
       <c r="V77" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="W77" s="4" t="s">
         <v>26</v>
@@ -12992,10 +13075,10 @@
         <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>26</v>
@@ -13007,43 +13090,43 @@
         <v>28</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L78" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="M78" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="O78" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="M78" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N78" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="O78" s="4" t="s">
-        <v>657</v>
-      </c>
       <c r="P78" s="4" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="Q78" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R78" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="S78" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="T78" s="4" t="s">
         <v>26</v>
@@ -13052,7 +13135,7 @@
         <v>2</v>
       </c>
       <c r="V78" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="W78" s="4" t="s">
         <v>26</v>
@@ -13066,7 +13149,7 @@
         <v>202</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>204</v>
@@ -13078,10 +13161,10 @@
         <v>28</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>26</v>
@@ -13093,7 +13176,7 @@
         <v>26</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M79" s="4" t="s">
         <v>26</v>
@@ -13102,16 +13185,16 @@
         <v>26</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="Q79" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R79" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="S79" s="4" t="s">
         <v>26</v>
@@ -13123,7 +13206,7 @@
         <v>16</v>
       </c>
       <c r="V79" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="W79" s="4" t="s">
         <v>26</v>
@@ -13137,7 +13220,7 @@
         <v>202</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>204</v>
@@ -13149,43 +13232,43 @@
         <v>28</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M80" s="4" t="s">
         <v>26</v>
       </c>
       <c r="N80" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O80" s="4" t="s">
         <v>26</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="Q80" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R80" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="S80" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="T80" s="4" t="s">
         <v>26</v>
@@ -13194,7 +13277,7 @@
         <v>9</v>
       </c>
       <c r="V80" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W80" s="4" t="s">
         <v>26</v>
@@ -13205,10 +13288,10 @@
         <v>79</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>26</v>
@@ -13220,43 +13303,43 @@
         <v>28</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M81" s="4" t="s">
         <v>26</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="Q81" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R81" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="S81" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="T81" s="4" t="s">
         <v>26</v>
@@ -13265,7 +13348,7 @@
         <v>12</v>
       </c>
       <c r="V81" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="W81" s="4" t="s">
         <v>26</v>
@@ -13276,10 +13359,10 @@
         <v>80</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>26</v>
@@ -13291,10 +13374,10 @@
         <v>28</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>26</v>
@@ -13306,7 +13389,7 @@
         <v>26</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M82" s="4" t="s">
         <v>26</v>
@@ -13318,16 +13401,16 @@
         <v>26</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="Q82" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R82" s="4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="S82" s="4" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="T82" s="4" t="s">
         <v>26</v>
@@ -13336,7 +13419,7 @@
         <v>13</v>
       </c>
       <c r="V82" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="W82" s="4" t="s">
         <v>26</v>
@@ -13347,10 +13430,10 @@
         <v>81</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>26</v>
@@ -13362,7 +13445,7 @@
         <v>28</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>26</v>
@@ -13389,13 +13472,13 @@
         <v>26</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="Q83" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R83" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="S83" s="4" t="s">
         <v>26</v>
@@ -13421,7 +13504,7 @@
         <v>222</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>26</v>
@@ -13433,10 +13516,10 @@
         <v>28</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>26</v>
@@ -13448,7 +13531,7 @@
         <v>26</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M84" s="4" t="s">
         <v>26</v>
@@ -13460,16 +13543,16 @@
         <v>26</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Q84" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R84" s="4" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="S84" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="T84" s="4" t="s">
         <v>26</v>
@@ -13478,7 +13561,7 @@
         <v>1</v>
       </c>
       <c r="V84" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="W84" s="4" t="s">
         <v>26</v>
@@ -13492,7 +13575,7 @@
         <v>222</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>26</v>
@@ -13507,7 +13590,7 @@
         <v>26</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>26</v>
@@ -13519,7 +13602,7 @@
         <v>26</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M85" s="4" t="s">
         <v>26</v>
@@ -13531,13 +13614,13 @@
         <v>26</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="Q85" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R85" s="4" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="S85" s="4" t="s">
         <v>26</v>
@@ -13549,7 +13632,7 @@
         <v>3</v>
       </c>
       <c r="V85" s="4" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="W85" s="4" t="s">
         <v>26</v>
@@ -13563,7 +13646,7 @@
         <v>222</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>26</v>
@@ -13575,10 +13658,10 @@
         <v>28</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="I86" s="4" t="s">
         <v>26</v>
@@ -13590,7 +13673,7 @@
         <v>26</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M86" s="4" t="s">
         <v>26</v>
@@ -13602,16 +13685,16 @@
         <v>26</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="Q86" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="R86" s="4" t="s">
         <v>26</v>
       </c>
       <c r="S86" s="4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="T86" s="4" t="s">
         <v>26</v>
@@ -13620,7 +13703,7 @@
         <v>8</v>
       </c>
       <c r="V86" s="4" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="W86" s="4" t="s">
         <v>26</v>
@@ -13634,7 +13717,7 @@
         <v>222</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>26</v>
@@ -13646,7 +13729,7 @@
         <v>28</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>26</v>
@@ -13673,7 +13756,7 @@
         <v>26</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="Q87" s="4" t="s">
         <v>26</v>
@@ -13705,7 +13788,7 @@
         <v>222</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>26</v>
@@ -13717,7 +13800,7 @@
         <v>28</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H88" s="4" t="s">
         <v>26</v>
@@ -13744,7 +13827,7 @@
         <v>26</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="Q88" s="4" t="s">
         <v>26</v>
@@ -13776,7 +13859,7 @@
         <v>222</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>26</v>
@@ -13788,10 +13871,10 @@
         <v>28</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>26</v>
@@ -13803,7 +13886,7 @@
         <v>26</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M89" s="4" t="s">
         <v>26</v>
@@ -13815,7 +13898,7 @@
         <v>26</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="Q89" s="4" t="s">
         <v>26</v>
@@ -13824,7 +13907,7 @@
         <v>26</v>
       </c>
       <c r="S89" s="4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="T89" s="4" t="s">
         <v>26</v>
@@ -13833,7 +13916,7 @@
         <v>9</v>
       </c>
       <c r="V89" s="4" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="W89" s="4" t="s">
         <v>26</v>
@@ -13847,7 +13930,7 @@
         <v>222</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>26</v>
@@ -13859,10 +13942,10 @@
         <v>28</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="I90" s="4" t="s">
         <v>26</v>
@@ -13874,28 +13957,28 @@
         <v>26</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="M90" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="N90" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="Q90" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R90" s="4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="S90" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="T90" s="4" t="s">
         <v>26</v>
@@ -13904,7 +13987,7 @@
         <v>10</v>
       </c>
       <c r="V90" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="W90" s="4" t="s">
         <v>26</v>
@@ -13918,7 +14001,7 @@
         <v>222</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>26</v>
@@ -13930,10 +14013,10 @@
         <v>28</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>26</v>
@@ -13942,10 +14025,10 @@
         <v>26</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M91" s="4" t="s">
         <v>26</v>
@@ -13957,16 +14040,16 @@
         <v>26</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="Q91" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R91" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="S91" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="T91" s="4" t="s">
         <v>26</v>
@@ -13975,7 +14058,7 @@
         <v>20</v>
       </c>
       <c r="V91" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="W91" s="4" t="s">
         <v>26</v>
@@ -13989,7 +14072,7 @@
         <v>222</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>26</v>
@@ -14001,22 +14084,22 @@
         <v>28</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M92" s="4" t="s">
         <v>26</v>
@@ -14025,10 +14108,10 @@
         <v>26</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="Q92" s="4" t="s">
         <v>359</v>
@@ -14037,7 +14120,7 @@
         <v>26</v>
       </c>
       <c r="S92" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="T92" s="4" t="s">
         <v>26</v>
@@ -14046,7 +14129,7 @@
         <v>2</v>
       </c>
       <c r="V92" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="W92" s="4" t="s">
         <v>26</v>
@@ -14057,10 +14140,10 @@
         <v>91</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>26</v>
@@ -14072,10 +14155,10 @@
         <v>28</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>26</v>
@@ -14084,31 +14167,31 @@
         <v>26</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="L93" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="M93" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N93" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O93" s="4" t="s">
         <v>780</v>
       </c>
-      <c r="M93" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N93" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O93" s="4" t="s">
-        <v>779</v>
-      </c>
       <c r="P93" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="Q93" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R93" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="S93" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="T93" s="4" t="s">
         <v>26</v>
@@ -14117,7 +14200,7 @@
         <v>13</v>
       </c>
       <c r="V93" s="4" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="W93" s="4" t="s">
         <v>26</v>
@@ -14128,10 +14211,10 @@
         <v>92</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>26</v>
@@ -14143,26 +14226,26 @@
         <v>28</v>
       </c>
       <c r="G94" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L94" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="M94" s="4" t="s">
         <v>787</v>
       </c>
-      <c r="H94" s="4" t="s">
-        <v>788</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J94" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L94" s="4" t="s">
-        <v>789</v>
-      </c>
-      <c r="M94" s="4" t="s">
-        <v>786</v>
-      </c>
       <c r="N94" s="4" t="s">
         <v>26</v>
       </c>
@@ -14170,7 +14253,7 @@
         <v>26</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="Q94" s="4" t="s">
         <v>26</v>
@@ -14179,7 +14262,7 @@
         <v>26</v>
       </c>
       <c r="S94" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="T94" s="4" t="s">
         <v>26</v>
@@ -14188,7 +14271,7 @@
         <v>10</v>
       </c>
       <c r="V94" s="4" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="W94" s="4" t="s">
         <v>26</v>
@@ -14199,10 +14282,10 @@
         <v>93</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>26</v>
@@ -14214,22 +14297,22 @@
         <v>28</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M95" s="4" t="s">
         <v>26</v>
@@ -14241,7 +14324,7 @@
         <v>26</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="Q95" s="4" t="s">
         <v>26</v>
@@ -14250,7 +14333,7 @@
         <v>26</v>
       </c>
       <c r="S95" s="4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="T95" s="4" t="s">
         <v>26</v>
@@ -14259,7 +14342,7 @@
         <v>16</v>
       </c>
       <c r="V95" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="W95" s="4" t="s">
         <v>26</v>
@@ -14270,10 +14353,10 @@
         <v>94</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>26</v>
@@ -14285,10 +14368,10 @@
         <v>28</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>26</v>
@@ -14297,10 +14380,10 @@
         <v>26</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M96" s="4" t="s">
         <v>26</v>
@@ -14312,7 +14395,7 @@
         <v>26</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="Q96" s="4" t="s">
         <v>26</v>
@@ -14321,7 +14404,7 @@
         <v>26</v>
       </c>
       <c r="S96" s="4" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="T96" s="4" t="s">
         <v>26</v>
@@ -14330,7 +14413,7 @@
         <v>32</v>
       </c>
       <c r="V96" s="4" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="W96" s="4" t="s">
         <v>26</v>
@@ -14344,7 +14427,7 @@
         <v>245</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>26</v>
@@ -14359,7 +14442,7 @@
         <v>26</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>26</v>
@@ -14368,10 +14451,10 @@
         <v>26</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="M97" s="4" t="s">
         <v>26</v>
@@ -14383,7 +14466,7 @@
         <v>26</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="Q97" s="4" t="s">
         <v>26</v>
@@ -14401,7 +14484,7 @@
         <v>2</v>
       </c>
       <c r="V97" s="4" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="W97" s="4" t="s">
         <v>26</v>
@@ -14415,7 +14498,7 @@
         <v>245</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>26</v>
@@ -14427,10 +14510,10 @@
         <v>28</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>26</v>
@@ -14439,10 +14522,10 @@
         <v>26</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="M98" s="4" t="s">
         <v>26</v>
@@ -14451,10 +14534,10 @@
         <v>26</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="Q98" s="4" t="s">
         <v>26</v>
@@ -14463,7 +14546,7 @@
         <v>26</v>
       </c>
       <c r="S98" s="4" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="T98" s="4" t="s">
         <v>26</v>
@@ -14472,7 +14555,7 @@
         <v>18</v>
       </c>
       <c r="V98" s="4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="W98" s="4" t="s">
         <v>26</v>
@@ -14486,7 +14569,7 @@
         <v>245</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>26</v>
@@ -14498,10 +14581,10 @@
         <v>28</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>26</v>
@@ -14510,10 +14593,10 @@
         <v>26</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="M99" s="4" t="s">
         <v>26</v>
@@ -14522,19 +14605,19 @@
         <v>26</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="Q99" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R99" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="S99" s="4" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="T99" s="4" t="s">
         <v>26</v>
@@ -14543,7 +14626,7 @@
         <v>6</v>
       </c>
       <c r="V99" s="4" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="W99" s="4" t="s">
         <v>26</v>
@@ -14557,7 +14640,7 @@
         <v>245</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>26</v>
@@ -14569,10 +14652,10 @@
         <v>28</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>26</v>
@@ -14581,10 +14664,10 @@
         <v>26</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M100" s="4" t="s">
         <v>26</v>
@@ -14593,10 +14676,10 @@
         <v>26</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="Q100" s="4" t="s">
         <v>26</v>
@@ -14605,7 +14688,7 @@
         <v>26</v>
       </c>
       <c r="S100" s="4" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="T100" s="4" t="s">
         <v>26</v>
@@ -14614,7 +14697,7 @@
         <v>7</v>
       </c>
       <c r="V100" s="4" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="W100" s="4" t="s">
         <v>26</v>
@@ -14628,7 +14711,7 @@
         <v>245</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>26</v>
@@ -14640,10 +14723,10 @@
         <v>28</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>26</v>
@@ -14652,10 +14735,10 @@
         <v>278</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="M101" s="4" t="s">
         <v>26</v>
@@ -14667,16 +14750,16 @@
         <v>26</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="Q101" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R101" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="S101" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="T101" s="4" t="s">
         <v>26</v>
@@ -14699,7 +14782,7 @@
         <v>264</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>26</v>
@@ -14711,10 +14794,10 @@
         <v>28</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>26</v>
@@ -14723,31 +14806,31 @@
         <v>26</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M102" s="4" t="s">
         <v>26</v>
       </c>
       <c r="N102" s="4" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="O102" s="4" t="s">
         <v>26</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="Q102" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R102" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="S102" s="4" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="T102" s="4" t="s">
         <v>26</v>
@@ -14756,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="V102" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="W102" s="4" t="s">
         <v>26</v>
@@ -14770,7 +14853,7 @@
         <v>296</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>26</v>
@@ -14782,7 +14865,7 @@
         <v>28</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>26</v>
@@ -14797,7 +14880,7 @@
         <v>26</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="M103" s="4" t="s">
         <v>26</v>
@@ -14809,7 +14892,7 @@
         <v>26</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="Q103" s="4" t="s">
         <v>26</v>
@@ -14818,7 +14901,7 @@
         <v>26</v>
       </c>
       <c r="S103" s="4" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="T103" s="4" t="s">
         <v>26</v>
@@ -14827,7 +14910,7 @@
         <v>16</v>
       </c>
       <c r="V103" s="4" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="W103" s="4" t="s">
         <v>26</v>
@@ -14838,10 +14921,10 @@
         <v>102</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>26</v>
@@ -14880,7 +14963,7 @@
         <v>26</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="Q104" s="4" t="s">
         <v>26</v>
@@ -14909,10 +14992,10 @@
         <v>103</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>26</v>
@@ -14924,10 +15007,10 @@
         <v>28</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>26</v>
@@ -14936,10 +15019,10 @@
         <v>26</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="M105" s="4" t="s">
         <v>26</v>
@@ -14951,7 +15034,7 @@
         <v>26</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="Q105" s="4" t="s">
         <v>26</v>
@@ -14969,7 +15052,7 @@
         <v>16</v>
       </c>
       <c r="V105" s="4" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="W105" s="4" t="s">
         <v>26</v>
@@ -14983,7 +15066,7 @@
         <v>309</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>320</v>
@@ -14995,22 +15078,22 @@
         <v>28</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="I106" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M106" s="4" t="s">
         <v>26</v>
@@ -15022,13 +15105,13 @@
         <v>26</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="Q106" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R106" s="4" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="S106" s="4" t="s">
         <v>26</v>
@@ -15037,10 +15120,10 @@
         <v>26</v>
       </c>
       <c r="U106" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V106" s="4" t="s">
-        <v>26</v>
+        <v>891</v>
       </c>
       <c r="W106" s="4" t="s">
         <v>26</v>
@@ -15054,7 +15137,7 @@
         <v>309</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>311</v>
@@ -15066,10 +15149,10 @@
         <v>28</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>26</v>
@@ -15078,10 +15161,10 @@
         <v>26</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="M107" s="4" t="s">
         <v>26</v>
@@ -15090,10 +15173,10 @@
         <v>26</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="Q107" s="4" t="s">
         <v>26</v>
@@ -15102,16 +15185,16 @@
         <v>26</v>
       </c>
       <c r="S107" s="4" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="T107" s="4" t="s">
         <v>26</v>
       </c>
       <c r="U107" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V107" s="4" t="s">
-        <v>26</v>
+        <v>900</v>
       </c>
       <c r="W107" s="4" t="s">
         <v>26</v>
@@ -15125,7 +15208,7 @@
         <v>333</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>26</v>
@@ -15137,10 +15220,10 @@
         <v>28</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>26</v>
@@ -15152,19 +15235,19 @@
         <v>26</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="M108" s="4" t="s">
         <v>26</v>
       </c>
       <c r="N108" s="4" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="O108" s="4" t="s">
         <v>26</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="Q108" s="4" t="s">
         <v>26</v>
@@ -15173,7 +15256,7 @@
         <v>26</v>
       </c>
       <c r="S108" s="4" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="T108" s="4" t="s">
         <v>26</v>
@@ -15182,7 +15265,7 @@
         <v>16</v>
       </c>
       <c r="V108" s="4" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="W108" s="4" t="s">
         <v>26</v>
@@ -15196,7 +15279,7 @@
         <v>341</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>26</v>
@@ -15267,7 +15350,7 @@
         <v>341</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>26</v>
@@ -15279,34 +15362,34 @@
         <v>28</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="I110" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="M110" s="4" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="N110" s="4" t="s">
         <v>26</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="Q110" s="4" t="s">
         <v>26</v>
@@ -15315,7 +15398,7 @@
         <v>26</v>
       </c>
       <c r="S110" s="4" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="T110" s="4" t="s">
         <v>26</v>
@@ -15324,7 +15407,7 @@
         <v>7</v>
       </c>
       <c r="V110" s="4" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="W110" s="4" t="s">
         <v>26</v>
@@ -15338,7 +15421,7 @@
         <v>341</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>26</v>
@@ -15350,22 +15433,22 @@
         <v>28</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="M111" s="4" t="s">
         <v>26</v>
@@ -15374,19 +15457,19 @@
         <v>26</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="Q111" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R111" s="4" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="S111" s="4" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="T111" s="4" t="s">
         <v>26</v>
@@ -15395,7 +15478,7 @@
         <v>21</v>
       </c>
       <c r="V111" s="4" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="W111" s="4" t="s">
         <v>26</v>
@@ -15409,7 +15492,7 @@
         <v>341</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>26</v>
@@ -15421,10 +15504,10 @@
         <v>28</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>26</v>
@@ -15436,10 +15519,10 @@
         <v>26</v>
       </c>
       <c r="L112" s="4" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="M112" s="4" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="N112" s="4" t="s">
         <v>26</v>
@@ -15448,7 +15531,7 @@
         <v>26</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="Q112" s="4" t="s">
         <v>26</v>
@@ -15457,7 +15540,7 @@
         <v>26</v>
       </c>
       <c r="S112" s="4" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="T112" s="4" t="s">
         <v>26</v>
@@ -15466,7 +15549,7 @@
         <v>17</v>
       </c>
       <c r="V112" s="4" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="W112" s="4" t="s">
         <v>26</v>
@@ -15480,7 +15563,7 @@
         <v>341</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>26</v>
@@ -15492,22 +15575,22 @@
         <v>28</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="M113" s="4" t="s">
         <v>26</v>
@@ -15516,19 +15599,19 @@
         <v>26</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="Q113" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R113" s="4" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="S113" s="4" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="T113" s="4" t="s">
         <v>26</v>
@@ -15537,7 +15620,7 @@
         <v>10</v>
       </c>
       <c r="V113" s="4" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="W113" s="4" t="s">
         <v>26</v>
@@ -15548,10 +15631,10 @@
         <v>112</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>26</v>
@@ -15566,7 +15649,7 @@
         <v>26</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>26</v>
@@ -15575,10 +15658,10 @@
         <v>26</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="M114" s="4" t="s">
         <v>26</v>
@@ -15590,13 +15673,13 @@
         <v>26</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="Q114" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R114" s="4" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="S114" s="4" t="s">
         <v>26</v>
@@ -15608,7 +15691,7 @@
         <v>8</v>
       </c>
       <c r="V114" s="4" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="W114" s="4" t="s">
         <v>26</v>
@@ -15622,7 +15705,7 @@
         <v>372</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>374</v>
@@ -15634,22 +15717,22 @@
         <v>28</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="K115" s="4" t="s">
         <v>26</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="M115" s="4" t="s">
         <v>26</v>
@@ -15661,7 +15744,7 @@
         <v>26</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="Q115" s="4" t="s">
         <v>26</v>
@@ -15670,16 +15753,16 @@
         <v>26</v>
       </c>
       <c r="S115" s="4" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="T115" s="4" t="s">
         <v>26</v>
       </c>
       <c r="U115" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V115" s="4" t="s">
-        <v>26</v>
+        <v>965</v>
       </c>
       <c r="W115" s="4" t="s">
         <v>26</v>
@@ -15693,7 +15776,7 @@
         <v>372</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>374</v>
@@ -15705,52 +15788,52 @@
         <v>28</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="M116" s="4" t="s">
         <v>26</v>
       </c>
       <c r="N116" s="4" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="O116" s="4" t="s">
         <v>26</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="Q116" s="4" t="s">
         <v>26</v>
       </c>
       <c r="R116" s="4" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="S116" s="4" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="T116" s="4" t="s">
         <v>26</v>
       </c>
       <c r="U116" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V116" s="4" t="s">
-        <v>26</v>
+        <v>976</v>
       </c>
       <c r="W116" s="4" t="s">
         <v>26</v>
@@ -15764,7 +15847,7 @@
         <v>372</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>374</v>
@@ -15776,10 +15859,10 @@
         <v>28</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>26</v>
@@ -15788,10 +15871,10 @@
         <v>26</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="M117" s="4" t="s">
         <v>26</v>
@@ -15800,10 +15883,10 @@
         <v>26</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="Q117" s="4" t="s">
         <v>26</v>
@@ -15812,7 +15895,7 @@
         <v>26</v>
       </c>
       <c r="S117" s="4" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="T117" s="4" t="s">
         <v>26</v>
@@ -15821,7 +15904,7 @@
         <v>14</v>
       </c>
       <c r="V117" s="4" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="W117" s="4" t="s">
         <v>26</v>
@@ -15835,13 +15918,13 @@
         <v>24</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>28</v>
@@ -15850,7 +15933,7 @@
         <v>26</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="I118" s="5" t="s">
         <v>26</v>
@@ -15859,10 +15942,10 @@
         <v>26</v>
       </c>
       <c r="K118" s="5" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="L118" s="5" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="M118" s="5" t="s">
         <v>26</v>
@@ -15874,7 +15957,7 @@
         <v>26</v>
       </c>
       <c r="P118" s="5" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="Q118" s="5" t="s">
         <v>26</v>
@@ -15883,7 +15966,7 @@
         <v>26</v>
       </c>
       <c r="S118" s="5" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="T118" s="5" t="s">
         <v>26</v>
@@ -15892,7 +15975,7 @@
         <v>1</v>
       </c>
       <c r="V118" s="5" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="W118" s="5" t="s">
         <v>26</v>
@@ -15906,13 +15989,13 @@
         <v>24</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>28</v>
@@ -15945,7 +16028,7 @@
         <v>26</v>
       </c>
       <c r="P119" s="5" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="Q119" s="5" t="s">
         <v>26</v>
@@ -15977,22 +16060,22 @@
         <v>24</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="I120" s="5" t="s">
         <v>26</v>
@@ -16004,7 +16087,7 @@
         <v>26</v>
       </c>
       <c r="L120" s="5" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="M120" s="5" t="s">
         <v>26</v>
@@ -16016,16 +16099,16 @@
         <v>26</v>
       </c>
       <c r="P120" s="5" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="Q120" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R120" s="5" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="S120" s="5" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="T120" s="5" t="s">
         <v>26</v>
@@ -16034,7 +16117,7 @@
         <v>5</v>
       </c>
       <c r="V120" s="5" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="W120" s="5" t="s">
         <v>26</v>
@@ -16048,22 +16131,22 @@
         <v>24</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="I121" s="5" t="s">
         <v>26</v>
@@ -16072,7 +16155,7 @@
         <v>26</v>
       </c>
       <c r="K121" s="5" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="L121" s="5" t="s">
         <v>26</v>
@@ -16087,7 +16170,7 @@
         <v>26</v>
       </c>
       <c r="P121" s="5" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="Q121" s="5" t="s">
         <v>26</v>
@@ -16096,7 +16179,7 @@
         <v>26</v>
       </c>
       <c r="S121" s="5" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="T121" s="5" t="s">
         <v>26</v>
@@ -16105,7 +16188,7 @@
         <v>3</v>
       </c>
       <c r="V121" s="5" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="W121" s="5" t="s">
         <v>26</v>
@@ -16119,13 +16202,13 @@
         <v>24</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>28</v>
@@ -16158,7 +16241,7 @@
         <v>26</v>
       </c>
       <c r="P122" s="5" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="Q122" s="5" t="s">
         <v>26</v>
@@ -16167,10 +16250,10 @@
         <v>26</v>
       </c>
       <c r="S122" s="5" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="T122" s="5" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="U122" s="5">
         <v>0</v>
@@ -16190,13 +16273,13 @@
         <v>67</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>28</v>
@@ -16205,40 +16288,40 @@
         <v>26</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="I123" s="5" t="s">
         <v>26</v>
       </c>
       <c r="J123" s="5" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="K123" s="5" t="s">
         <v>26</v>
       </c>
       <c r="L123" s="5" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="M123" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N123" s="5" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="O123" s="5" t="s">
         <v>26</v>
       </c>
       <c r="P123" s="5" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="Q123" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R123" s="5" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="S123" s="5" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="T123" s="5" t="s">
         <v>26</v>
@@ -16247,7 +16330,7 @@
         <v>2</v>
       </c>
       <c r="V123" s="5" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="W123" s="5" t="s">
         <v>26</v>
@@ -16261,13 +16344,13 @@
         <v>67</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>28</v>
@@ -16276,7 +16359,7 @@
         <v>26</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="I124" s="5" t="s">
         <v>26</v>
@@ -16285,10 +16368,10 @@
         <v>26</v>
       </c>
       <c r="K124" s="5" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="L124" s="5" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="M124" s="5" t="s">
         <v>26</v>
@@ -16297,10 +16380,10 @@
         <v>26</v>
       </c>
       <c r="O124" s="5" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="P124" s="5" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="Q124" s="5" t="s">
         <v>26</v>
@@ -16309,7 +16392,7 @@
         <v>26</v>
       </c>
       <c r="S124" s="5" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="T124" s="5" t="s">
         <v>26</v>
@@ -16318,7 +16401,7 @@
         <v>4</v>
       </c>
       <c r="V124" s="5" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="W124" s="5" t="s">
         <v>26</v>
@@ -16332,13 +16415,13 @@
         <v>67</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>28</v>
@@ -16359,7 +16442,7 @@
         <v>26</v>
       </c>
       <c r="L125" s="5" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="M125" s="5" t="s">
         <v>26</v>
@@ -16368,19 +16451,19 @@
         <v>26</v>
       </c>
       <c r="O125" s="5" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="P125" s="5" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="Q125" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R125" s="5" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="S125" s="5" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="T125" s="5" t="s">
         <v>26</v>
@@ -16403,13 +16486,13 @@
         <v>67</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>28</v>
@@ -16442,13 +16525,13 @@
         <v>26</v>
       </c>
       <c r="P126" s="5" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="Q126" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R126" s="5" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="S126" s="5" t="s">
         <v>26</v>
@@ -16474,13 +16557,13 @@
         <v>67</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>28</v>
@@ -16489,7 +16572,7 @@
         <v>26</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="I127" s="5" t="s">
         <v>26</v>
@@ -16501,7 +16584,7 @@
         <v>26</v>
       </c>
       <c r="L127" s="5" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="M127" s="5" t="s">
         <v>26</v>
@@ -16513,13 +16596,13 @@
         <v>26</v>
       </c>
       <c r="P127" s="5" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="Q127" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R127" s="5" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="S127" s="5" t="s">
         <v>26</v>
@@ -16531,7 +16614,7 @@
         <v>1</v>
       </c>
       <c r="V127" s="5" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="W127" s="5" t="s">
         <v>26</v>
@@ -16545,13 +16628,13 @@
         <v>67</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>28</v>
@@ -16560,7 +16643,7 @@
         <v>26</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="I128" s="5" t="s">
         <v>26</v>
@@ -16569,13 +16652,13 @@
         <v>26</v>
       </c>
       <c r="K128" s="5" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="L128" s="5" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="M128" s="5" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="N128" s="5" t="s">
         <v>26</v>
@@ -16584,7 +16667,7 @@
         <v>26</v>
       </c>
       <c r="P128" s="5" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="Q128" s="5" t="s">
         <v>26</v>
@@ -16616,13 +16699,13 @@
         <v>67</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>28</v>
@@ -16643,7 +16726,7 @@
         <v>26</v>
       </c>
       <c r="L129" s="5" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="M129" s="5" t="s">
         <v>26</v>
@@ -16655,7 +16738,7 @@
         <v>26</v>
       </c>
       <c r="P129" s="5" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="Q129" s="5" t="s">
         <v>26</v>
@@ -16687,52 +16770,52 @@
         <v>67</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="I130" s="5" t="s">
         <v>26</v>
       </c>
       <c r="J130" s="5" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="K130" s="5" t="s">
         <v>26</v>
       </c>
       <c r="L130" s="5" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="M130" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N130" s="5" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="O130" s="5" t="s">
         <v>26</v>
       </c>
       <c r="P130" s="5" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="Q130" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R130" s="5" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="S130" s="5" t="s">
         <v>26</v>
@@ -16744,7 +16827,7 @@
         <v>8</v>
       </c>
       <c r="V130" s="5" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="W130" s="5" t="s">
         <v>26</v>
@@ -16758,13 +16841,13 @@
         <v>139</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>28</v>
@@ -16773,19 +16856,19 @@
         <v>26</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="I131" s="5" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="J131" s="5" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="K131" s="5" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="L131" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="M131" s="5" t="s">
         <v>26</v>
@@ -16794,28 +16877,28 @@
         <v>26</v>
       </c>
       <c r="O131" s="5" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="P131" s="5" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="Q131" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R131" s="5" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="S131" s="5" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="T131" s="5" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="U131" s="5">
         <v>1</v>
       </c>
       <c r="V131" s="5" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="W131" s="5" t="s">
         <v>26</v>
@@ -16829,19 +16912,19 @@
         <v>139</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="H132" s="5" t="s">
         <v>26</v>
@@ -16868,7 +16951,7 @@
         <v>26</v>
       </c>
       <c r="P132" s="5" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="Q132" s="5" t="s">
         <v>26</v>
@@ -16900,34 +16983,34 @@
         <v>139</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="I133" s="5" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="J133" s="5" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="K133" s="5" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="L133" s="5" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="M133" s="5" t="s">
         <v>26</v>
@@ -16939,16 +17022,16 @@
         <v>26</v>
       </c>
       <c r="P133" s="5" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="Q133" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R133" s="5" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="S133" s="5" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="T133" s="5" t="s">
         <v>26</v>
@@ -16957,7 +17040,7 @@
         <v>13</v>
       </c>
       <c r="V133" s="5" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="W133" s="5" t="s">
         <v>26</v>
@@ -16971,13 +17054,13 @@
         <v>154</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="D134" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>28</v>
@@ -16986,7 +17069,7 @@
         <v>26</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="I134" s="5" t="s">
         <v>26</v>
@@ -16995,10 +17078,10 @@
         <v>26</v>
       </c>
       <c r="K134" s="5" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="L134" s="5" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="M134" s="5" t="s">
         <v>26</v>
@@ -17007,19 +17090,19 @@
         <v>26</v>
       </c>
       <c r="O134" s="5" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="P134" s="5" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="Q134" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R134" s="5" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="S134" s="5" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="T134" s="5" t="s">
         <v>26</v>
@@ -17028,7 +17111,7 @@
         <v>1</v>
       </c>
       <c r="V134" s="5" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="W134" s="5" t="s">
         <v>26</v>
@@ -17042,19 +17125,19 @@
         <v>154</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="H135" s="5" t="s">
         <v>26</v>
@@ -17081,7 +17164,7 @@
         <v>26</v>
       </c>
       <c r="P135" s="5" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="Q135" s="5" t="s">
         <v>26</v>
@@ -17090,7 +17173,7 @@
         <v>26</v>
       </c>
       <c r="S135" s="5" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="T135" s="5" t="s">
         <v>26</v>
@@ -17099,7 +17182,7 @@
         <v>2</v>
       </c>
       <c r="V135" s="5" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="W135" s="5" t="s">
         <v>26</v>
@@ -17110,37 +17193,37 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="D136" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="I136" s="5" t="s">
         <v>26</v>
       </c>
       <c r="J136" s="5" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="K136" s="5" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="L136" s="5" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="M136" s="5" t="s">
         <v>26</v>
@@ -17149,10 +17232,10 @@
         <v>26</v>
       </c>
       <c r="O136" s="5" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="P136" s="5" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="Q136" s="5" t="s">
         <v>26</v>
@@ -17161,7 +17244,7 @@
         <v>26</v>
       </c>
       <c r="S136" s="5" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="T136" s="5" t="s">
         <v>26</v>
@@ -17170,7 +17253,7 @@
         <v>9</v>
       </c>
       <c r="V136" s="5" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="W136" s="5" t="s">
         <v>26</v>
@@ -17184,22 +17267,22 @@
         <v>202</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>204</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>26</v>
@@ -17211,7 +17294,7 @@
         <v>26</v>
       </c>
       <c r="L137" s="5" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="M137" s="5" t="s">
         <v>26</v>
@@ -17220,10 +17303,10 @@
         <v>26</v>
       </c>
       <c r="O137" s="5" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="P137" s="5" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="Q137" s="5" t="s">
         <v>26</v>
@@ -17232,16 +17315,16 @@
         <v>26</v>
       </c>
       <c r="S137" s="5" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="T137" s="5" t="s">
         <v>26</v>
       </c>
       <c r="U137" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V137" s="5" t="s">
-        <v>26</v>
+        <v>1118</v>
       </c>
       <c r="W137" s="5" t="s">
         <v>26</v>
@@ -17255,34 +17338,34 @@
         <v>202</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="I138" s="5" t="s">
         <v>26</v>
       </c>
       <c r="J138" s="5" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="K138" s="5" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="L138" s="5" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="M138" s="5" t="s">
         <v>26</v>
@@ -17294,16 +17377,16 @@
         <v>26</v>
       </c>
       <c r="P138" s="5" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="Q138" s="5" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="R138" s="5" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="S138" s="5" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="T138" s="5" t="s">
         <v>26</v>
@@ -17312,7 +17395,7 @@
         <v>11</v>
       </c>
       <c r="V138" s="5" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="W138" s="5" t="s">
         <v>26</v>
@@ -17326,13 +17409,13 @@
         <v>202</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>204</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>28</v>
@@ -17341,19 +17424,19 @@
         <v>26</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="I139" s="5" t="s">
         <v>26</v>
       </c>
       <c r="J139" s="5" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="K139" s="5" t="s">
         <v>26</v>
       </c>
       <c r="L139" s="5" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="M139" s="5" t="s">
         <v>26</v>
@@ -17365,13 +17448,13 @@
         <v>26</v>
       </c>
       <c r="P139" s="5" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="Q139" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R139" s="5" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="S139" s="5" t="s">
         <v>26</v>
@@ -17380,10 +17463,10 @@
         <v>26</v>
       </c>
       <c r="U139" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V139" s="5" t="s">
-        <v>26</v>
+        <v>1136</v>
       </c>
       <c r="W139" s="5" t="s">
         <v>26</v>
@@ -17397,13 +17480,13 @@
         <v>202</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>204</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>28</v>
@@ -17412,10 +17495,10 @@
         <v>26</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>1131</v>
+        <v>1138</v>
       </c>
       <c r="I140" s="5" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="J140" s="5" t="s">
         <v>26</v>
@@ -17424,7 +17507,7 @@
         <v>26</v>
       </c>
       <c r="L140" s="5" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
       <c r="M140" s="5" t="s">
         <v>26</v>
@@ -17436,7 +17519,7 @@
         <v>26</v>
       </c>
       <c r="P140" s="5" t="s">
-        <v>1134</v>
+        <v>1141</v>
       </c>
       <c r="Q140" s="5" t="s">
         <v>26</v>
@@ -17451,10 +17534,10 @@
         <v>26</v>
       </c>
       <c r="U140" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V140" s="5" t="s">
-        <v>26</v>
+        <v>1142</v>
       </c>
       <c r="W140" s="5" t="s">
         <v>26</v>
@@ -17468,13 +17551,13 @@
         <v>222</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>28</v>
@@ -17483,7 +17566,7 @@
         <v>26</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="I141" s="5" t="s">
         <v>26</v>
@@ -17495,7 +17578,7 @@
         <v>26</v>
       </c>
       <c r="L141" s="5" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="M141" s="5" t="s">
         <v>26</v>
@@ -17507,7 +17590,7 @@
         <v>26</v>
       </c>
       <c r="P141" s="5" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="Q141" s="5" t="s">
         <v>26</v>
@@ -17525,7 +17608,7 @@
         <v>1</v>
       </c>
       <c r="V141" s="5" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="W141" s="5" t="s">
         <v>26</v>
@@ -17539,46 +17622,46 @@
         <v>222</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="I142" s="5" t="s">
         <v>26</v>
       </c>
       <c r="J142" s="5" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="K142" s="5" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="L142" s="5" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="M142" s="5" t="s">
         <v>359</v>
       </c>
       <c r="N142" s="5" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="O142" s="5" t="s">
         <v>26</v>
       </c>
       <c r="P142" s="5" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="Q142" s="5" t="s">
         <v>26</v>
@@ -17596,7 +17679,7 @@
         <v>9</v>
       </c>
       <c r="V142" s="5" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="W142" s="5" t="s">
         <v>26</v>
@@ -17610,13 +17693,13 @@
         <v>222</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>28</v>
@@ -17625,7 +17708,7 @@
         <v>26</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="I143" s="5" t="s">
         <v>26</v>
@@ -17637,7 +17720,7 @@
         <v>26</v>
       </c>
       <c r="L143" s="5" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="M143" s="5" t="s">
         <v>26</v>
@@ -17649,16 +17732,16 @@
         <v>26</v>
       </c>
       <c r="P143" s="5" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="Q143" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R143" s="5" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="S143" s="5" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="T143" s="5" t="s">
         <v>26</v>
@@ -17667,7 +17750,7 @@
         <v>1</v>
       </c>
       <c r="V143" s="5" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="W143" s="5" t="s">
         <v>26</v>
@@ -17681,22 +17764,22 @@
         <v>222</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="I144" s="5" t="s">
         <v>26</v>
@@ -17708,7 +17791,7 @@
         <v>26</v>
       </c>
       <c r="L144" s="5" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="M144" s="5" t="s">
         <v>26</v>
@@ -17720,7 +17803,7 @@
         <v>26</v>
       </c>
       <c r="P144" s="5" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="Q144" s="5" t="s">
         <v>26</v>
@@ -17729,7 +17812,7 @@
         <v>26</v>
       </c>
       <c r="S144" s="5" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="T144" s="5" t="s">
         <v>26</v>
@@ -17738,7 +17821,7 @@
         <v>10</v>
       </c>
       <c r="V144" s="5" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
       <c r="W144" s="5" t="s">
         <v>26</v>
@@ -17752,46 +17835,46 @@
         <v>222</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="I145" s="5" t="s">
         <v>26</v>
       </c>
       <c r="J145" s="5" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="K145" s="5" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="L145" s="5" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="M145" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N145" s="5" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="O145" s="5" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="P145" s="5" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="Q145" s="5" t="s">
         <v>26</v>
@@ -17809,7 +17892,7 @@
         <v>11</v>
       </c>
       <c r="V145" s="5" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="W145" s="5" t="s">
         <v>26</v>
@@ -17820,25 +17903,25 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="I146" s="5" t="s">
         <v>26</v>
@@ -17850,19 +17933,19 @@
         <v>26</v>
       </c>
       <c r="L146" s="5" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="M146" s="5" t="s">
         <v>359</v>
       </c>
       <c r="N146" s="5" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="O146" s="5" t="s">
         <v>26</v>
       </c>
       <c r="P146" s="5" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="Q146" s="5" t="s">
         <v>26</v>
@@ -17871,7 +17954,7 @@
         <v>26</v>
       </c>
       <c r="S146" s="5" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="T146" s="5" t="s">
         <v>26</v>
@@ -17880,7 +17963,7 @@
         <v>13</v>
       </c>
       <c r="V146" s="5" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="W146" s="5" t="s">
         <v>26</v>
@@ -17894,13 +17977,13 @@
         <v>239</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>28</v>
@@ -17951,7 +18034,7 @@
         <v>1</v>
       </c>
       <c r="V147" s="5" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="W147" s="5" t="s">
         <v>26</v>
@@ -17965,34 +18048,34 @@
         <v>239</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="I148" s="5" t="s">
         <v>26</v>
       </c>
       <c r="J148" s="5" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="K148" s="5" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="L148" s="5" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="M148" s="5" t="s">
         <v>26</v>
@@ -18001,10 +18084,10 @@
         <v>26</v>
       </c>
       <c r="O148" s="5" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="P148" s="5" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="Q148" s="5" t="s">
         <v>26</v>
@@ -18013,7 +18096,7 @@
         <v>26</v>
       </c>
       <c r="S148" s="5" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="T148" s="5" t="s">
         <v>26</v>
@@ -18022,7 +18105,7 @@
         <v>10</v>
       </c>
       <c r="V148" s="5" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="W148" s="5" t="s">
         <v>26</v>
@@ -18036,34 +18119,34 @@
         <v>264</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="I149" s="5" t="s">
         <v>26</v>
       </c>
       <c r="J149" s="5" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="K149" s="5" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="L149" s="5" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="M149" s="5" t="s">
         <v>26</v>
@@ -18072,10 +18155,10 @@
         <v>26</v>
       </c>
       <c r="O149" s="5" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="P149" s="5" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="Q149" s="5" t="s">
         <v>26</v>
@@ -18084,7 +18167,7 @@
         <v>26</v>
       </c>
       <c r="S149" s="5" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="T149" s="5" t="s">
         <v>26</v>
@@ -18093,7 +18176,7 @@
         <v>13</v>
       </c>
       <c r="V149" s="5" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="W149" s="5" t="s">
         <v>26</v>
@@ -18107,22 +18190,22 @@
         <v>24</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="I150" s="6" t="s">
         <v>26</v>
@@ -18131,10 +18214,10 @@
         <v>26</v>
       </c>
       <c r="K150" s="6" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="L150" s="6" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="M150" s="6" t="s">
         <v>26</v>
@@ -18143,10 +18226,10 @@
         <v>26</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="Q150" s="6" t="s">
         <v>26</v>
@@ -18155,16 +18238,16 @@
         <v>26</v>
       </c>
       <c r="S150" s="6" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="T150" s="6" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="U150" s="6">
         <v>7</v>
       </c>
       <c r="V150" s="6" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="W150" s="6" t="s">
         <v>26</v>
@@ -18178,22 +18261,22 @@
         <v>24</v>
       </c>
       <c r="C151" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E151" s="6" t="s">
         <v>1212</v>
-      </c>
-      <c r="D151" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E151" s="6" t="s">
-        <v>1204</v>
       </c>
       <c r="F151" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G151" s="6" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="H151" s="6" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="I151" s="6" t="s">
         <v>26</v>
@@ -18205,7 +18288,7 @@
         <v>26</v>
       </c>
       <c r="L151" s="6" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="M151" s="6" t="s">
         <v>26</v>
@@ -18214,10 +18297,10 @@
         <v>26</v>
       </c>
       <c r="O151" s="6" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="P151" s="6" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="Q151" s="6" t="s">
         <v>26</v>
@@ -18226,16 +18309,16 @@
         <v>26</v>
       </c>
       <c r="S151" s="6" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="T151" s="6" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="U151" s="6">
         <v>8</v>
       </c>
       <c r="V151" s="6" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="W151" s="6" t="s">
         <v>26</v>
@@ -18249,22 +18332,22 @@
         <v>431</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="I152" s="6" t="s">
         <v>26</v>
@@ -18273,10 +18356,10 @@
         <v>26</v>
       </c>
       <c r="K152" s="6" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="L152" s="6" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="M152" s="6" t="s">
         <v>26</v>
@@ -18285,10 +18368,10 @@
         <v>26</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="Q152" s="6" t="s">
         <v>26</v>
@@ -18306,7 +18389,7 @@
         <v>13</v>
       </c>
       <c r="V152" s="6" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="W152" s="6" t="s">
         <v>26</v>
@@ -18320,52 +18403,52 @@
         <v>125</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="D153" s="6" t="s">
         <v>127</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F153" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G153" s="6" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="H153" s="6" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="I153" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J153" s="6" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="K153" s="6" t="s">
         <v>26</v>
       </c>
       <c r="L153" s="6" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="M153" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N153" s="6" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="O153" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P153" s="6" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="Q153" s="6" t="s">
         <v>26</v>
       </c>
       <c r="R153" s="6" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="S153" s="6" t="s">
         <v>26</v>
@@ -18374,10 +18457,10 @@
         <v>26</v>
       </c>
       <c r="U153" s="6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V153" s="6" t="s">
-        <v>26</v>
+        <v>1242</v>
       </c>
       <c r="W153" s="6" t="s">
         <v>26</v>
@@ -18391,22 +18474,22 @@
         <v>171</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>1234</v>
+        <v>1243</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>1235</v>
+        <v>1244</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>1236</v>
+        <v>1245</v>
       </c>
       <c r="I154" s="6" t="s">
         <v>26</v>
@@ -18418,19 +18501,19 @@
         <v>26</v>
       </c>
       <c r="L154" s="6" t="s">
-        <v>1237</v>
+        <v>1246</v>
       </c>
       <c r="M154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>1238</v>
+        <v>1247</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>1239</v>
+        <v>1248</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>1240</v>
+        <v>1249</v>
       </c>
       <c r="Q154" s="6" t="s">
         <v>26</v>
@@ -18439,7 +18522,7 @@
         <v>26</v>
       </c>
       <c r="S154" s="6" t="s">
-        <v>1241</v>
+        <v>1250</v>
       </c>
       <c r="T154" s="6" t="s">
         <v>26</v>
@@ -18448,7 +18531,7 @@
         <v>7</v>
       </c>
       <c r="V154" s="6" t="s">
-        <v>1242</v>
+        <v>1251</v>
       </c>
       <c r="W154" s="6" t="s">
         <v>26</v>
@@ -18462,22 +18545,22 @@
         <v>171</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>1243</v>
+        <v>1252</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F155" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>1244</v>
+        <v>1253</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>1245</v>
+        <v>1254</v>
       </c>
       <c r="I155" s="6" t="s">
         <v>26</v>
@@ -18489,7 +18572,7 @@
         <v>26</v>
       </c>
       <c r="L155" s="6" t="s">
-        <v>1246</v>
+        <v>1255</v>
       </c>
       <c r="M155" s="6" t="s">
         <v>26</v>
@@ -18498,28 +18581,28 @@
         <v>26</v>
       </c>
       <c r="O155" s="6" t="s">
-        <v>1247</v>
+        <v>1256</v>
       </c>
       <c r="P155" s="6" t="s">
-        <v>1248</v>
+        <v>1257</v>
       </c>
       <c r="Q155" s="6" t="s">
-        <v>1249</v>
+        <v>1258</v>
       </c>
       <c r="R155" s="6" t="s">
         <v>26</v>
       </c>
       <c r="S155" s="6" t="s">
-        <v>1250</v>
+        <v>1259</v>
       </c>
       <c r="T155" s="6" t="s">
-        <v>1251</v>
+        <v>1260</v>
       </c>
       <c r="U155" s="6">
         <v>8</v>
       </c>
       <c r="V155" s="6" t="s">
-        <v>1252</v>
+        <v>1261</v>
       </c>
       <c r="W155" s="6" t="s">
         <v>26</v>
@@ -18533,22 +18616,22 @@
         <v>182</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>1253</v>
+        <v>1262</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>1254</v>
+        <v>1263</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>1255</v>
+        <v>1264</v>
       </c>
       <c r="I156" s="6" t="s">
         <v>26</v>
@@ -18557,10 +18640,10 @@
         <v>26</v>
       </c>
       <c r="K156" s="6" t="s">
-        <v>1256</v>
+        <v>1265</v>
       </c>
       <c r="L156" s="6" t="s">
-        <v>1257</v>
+        <v>1266</v>
       </c>
       <c r="M156" s="6" t="s">
         <v>26</v>
@@ -18572,25 +18655,25 @@
         <v>26</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>1258</v>
+        <v>1267</v>
       </c>
       <c r="Q156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="R156" s="6" t="s">
-        <v>1259</v>
+        <v>1268</v>
       </c>
       <c r="S156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="T156" s="6" t="s">
-        <v>1260</v>
+        <v>1269</v>
       </c>
       <c r="U156" s="6">
         <v>8</v>
       </c>
       <c r="V156" s="6" t="s">
-        <v>1261</v>
+        <v>1270</v>
       </c>
       <c r="W156" s="6" t="s">
         <v>26</v>
@@ -18604,22 +18687,22 @@
         <v>182</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>1262</v>
+        <v>1271</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F157" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>1263</v>
+        <v>1272</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>1264</v>
+        <v>1273</v>
       </c>
       <c r="I157" s="6" t="s">
         <v>26</v>
@@ -18643,7 +18726,7 @@
         <v>26</v>
       </c>
       <c r="P157" s="6" t="s">
-        <v>1265</v>
+        <v>1274</v>
       </c>
       <c r="Q157" s="6" t="s">
         <v>26</v>
@@ -18652,7 +18735,7 @@
         <v>26</v>
       </c>
       <c r="S157" s="6" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="T157" s="6" t="s">
         <v>26</v>
@@ -18661,7 +18744,7 @@
         <v>5</v>
       </c>
       <c r="V157" s="6" t="s">
-        <v>1267</v>
+        <v>1276</v>
       </c>
       <c r="W157" s="6" t="s">
         <v>26</v>
@@ -18675,34 +18758,34 @@
         <v>182</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>1268</v>
+        <v>1277</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>1269</v>
+        <v>1278</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>1270</v>
+        <v>1279</v>
       </c>
       <c r="I158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J158" s="6" t="s">
-        <v>1271</v>
+        <v>1280</v>
       </c>
       <c r="K158" s="6" t="s">
-        <v>1272</v>
+        <v>1281</v>
       </c>
       <c r="L158" s="6" t="s">
-        <v>1273</v>
+        <v>1282</v>
       </c>
       <c r="M158" s="6" t="s">
         <v>26</v>
@@ -18711,10 +18794,10 @@
         <v>26</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>1274</v>
+        <v>1283</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>1275</v>
+        <v>1284</v>
       </c>
       <c r="Q158" s="6" t="s">
         <v>26</v>
@@ -18723,7 +18806,7 @@
         <v>26</v>
       </c>
       <c r="S158" s="6" t="s">
-        <v>1276</v>
+        <v>1285</v>
       </c>
       <c r="T158" s="6" t="s">
         <v>26</v>
@@ -18732,7 +18815,7 @@
         <v>14</v>
       </c>
       <c r="V158" s="6" t="s">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="W158" s="6" t="s">
         <v>26</v>
@@ -18746,64 +18829,64 @@
         <v>182</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>1278</v>
+        <v>1287</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F159" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>1279</v>
+        <v>1288</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>1280</v>
+        <v>1289</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>1281</v>
+        <v>1290</v>
       </c>
       <c r="J159" s="6" t="s">
-        <v>1282</v>
+        <v>1291</v>
       </c>
       <c r="K159" s="6" t="s">
-        <v>1283</v>
+        <v>1292</v>
       </c>
       <c r="L159" s="6" t="s">
-        <v>1284</v>
+        <v>1293</v>
       </c>
       <c r="M159" s="6" t="s">
-        <v>1285</v>
+        <v>1294</v>
       </c>
       <c r="N159" s="6" t="s">
-        <v>1286</v>
+        <v>1295</v>
       </c>
       <c r="O159" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P159" s="6" t="s">
-        <v>1287</v>
+        <v>1296</v>
       </c>
       <c r="Q159" s="6" t="s">
         <v>26</v>
       </c>
       <c r="R159" s="6" t="s">
-        <v>1288</v>
+        <v>1297</v>
       </c>
       <c r="S159" s="6" t="s">
-        <v>1289</v>
+        <v>1298</v>
       </c>
       <c r="T159" s="6" t="s">
-        <v>1290</v>
+        <v>1299</v>
       </c>
       <c r="U159" s="6">
         <v>12</v>
       </c>
       <c r="V159" s="6" t="s">
-        <v>1291</v>
+        <v>1300</v>
       </c>
       <c r="W159" s="6" t="s">
         <v>26</v>
@@ -18814,49 +18897,49 @@
         <v>158</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>1292</v>
+        <v>1301</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>1293</v>
+        <v>1302</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>1294</v>
+        <v>1303</v>
       </c>
       <c r="I160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J160" s="6" t="s">
-        <v>1295</v>
+        <v>1304</v>
       </c>
       <c r="K160" s="6" t="s">
-        <v>1296</v>
+        <v>1305</v>
       </c>
       <c r="L160" s="6" t="s">
-        <v>1297</v>
+        <v>1306</v>
       </c>
       <c r="M160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>1298</v>
+        <v>1307</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>1299</v>
+        <v>1308</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>1300</v>
+        <v>1309</v>
       </c>
       <c r="Q160" s="6" t="s">
         <v>26</v>
@@ -18868,13 +18951,13 @@
         <v>26</v>
       </c>
       <c r="T160" s="6" t="s">
-        <v>1301</v>
+        <v>1310</v>
       </c>
       <c r="U160" s="6">
         <v>16</v>
       </c>
       <c r="V160" s="6" t="s">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="W160" s="6" t="s">
         <v>26</v>
@@ -18888,34 +18971,34 @@
         <v>202</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>1303</v>
+        <v>1312</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>204</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F161" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G161" s="6" t="s">
-        <v>1304</v>
+        <v>1313</v>
       </c>
       <c r="H161" s="6" t="s">
-        <v>1305</v>
+        <v>1314</v>
       </c>
       <c r="I161" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J161" s="6" t="s">
-        <v>1306</v>
+        <v>1315</v>
       </c>
       <c r="K161" s="6" t="s">
-        <v>1307</v>
+        <v>1316</v>
       </c>
       <c r="L161" s="6" t="s">
-        <v>1308</v>
+        <v>1317</v>
       </c>
       <c r="M161" s="6" t="s">
         <v>26</v>
@@ -18927,7 +19010,7 @@
         <v>26</v>
       </c>
       <c r="P161" s="6" t="s">
-        <v>1309</v>
+        <v>1318</v>
       </c>
       <c r="Q161" s="6" t="s">
         <v>26</v>
@@ -18939,13 +19022,13 @@
         <v>26</v>
       </c>
       <c r="T161" s="6" t="s">
-        <v>1310</v>
+        <v>1319</v>
       </c>
       <c r="U161" s="6">
         <v>15</v>
       </c>
       <c r="V161" s="6" t="s">
-        <v>1311</v>
+        <v>1320</v>
       </c>
       <c r="W161" s="6" t="s">
         <v>26</v>
@@ -18959,46 +19042,46 @@
         <v>202</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>1312</v>
+        <v>1321</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>204</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>1313</v>
+        <v>1322</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>1314</v>
+        <v>1323</v>
       </c>
       <c r="I162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J162" s="6" t="s">
-        <v>1315</v>
+        <v>1324</v>
       </c>
       <c r="K162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="L162" s="6" t="s">
-        <v>1316</v>
+        <v>1325</v>
       </c>
       <c r="M162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>1319</v>
+        <v>1328</v>
       </c>
       <c r="Q162" s="6" t="s">
         <v>26</v>
@@ -19013,10 +19096,10 @@
         <v>26</v>
       </c>
       <c r="U162" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V162" s="6" t="s">
-        <v>26</v>
+        <v>1329</v>
       </c>
       <c r="W162" s="6" t="s">
         <v>26</v>
@@ -19030,46 +19113,46 @@
         <v>202</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>1320</v>
+        <v>1330</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F163" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G163" s="6" t="s">
-        <v>1321</v>
+        <v>1331</v>
       </c>
       <c r="H163" s="6" t="s">
-        <v>1322</v>
+        <v>1332</v>
       </c>
       <c r="I163" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J163" s="6" t="s">
-        <v>1323</v>
+        <v>1333</v>
       </c>
       <c r="K163" s="6" t="s">
-        <v>1324</v>
+        <v>1334</v>
       </c>
       <c r="L163" s="6" t="s">
-        <v>1325</v>
+        <v>1335</v>
       </c>
       <c r="M163" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N163" s="6" t="s">
-        <v>1326</v>
+        <v>1336</v>
       </c>
       <c r="O163" s="6" t="s">
-        <v>1327</v>
+        <v>1337</v>
       </c>
       <c r="P163" s="6" t="s">
-        <v>1328</v>
+        <v>1338</v>
       </c>
       <c r="Q163" s="6" t="s">
         <v>26</v>
@@ -19081,13 +19164,13 @@
         <v>26</v>
       </c>
       <c r="T163" s="6" t="s">
-        <v>1329</v>
+        <v>1339</v>
       </c>
       <c r="U163" s="6">
         <v>24</v>
       </c>
       <c r="V163" s="6" t="s">
-        <v>1330</v>
+        <v>1340</v>
       </c>
       <c r="W163" s="6" t="s">
         <v>26</v>
@@ -19098,34 +19181,34 @@
         <v>162</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>1331</v>
+        <v>1341</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>1332</v>
+        <v>1342</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>1333</v>
+        <v>1343</v>
       </c>
       <c r="I164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J164" s="6" t="s">
-        <v>1334</v>
+        <v>1344</v>
       </c>
       <c r="K164" s="6" t="s">
-        <v>1335</v>
+        <v>1345</v>
       </c>
       <c r="L164" s="6" t="s">
         <v>26</v>
@@ -19158,7 +19241,7 @@
         <v>7</v>
       </c>
       <c r="V164" s="6" t="s">
-        <v>1336</v>
+        <v>1346</v>
       </c>
       <c r="W164" s="6" t="s">
         <v>26</v>
@@ -19172,22 +19255,22 @@
         <v>222</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>1337</v>
+        <v>1347</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F165" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G165" s="6" t="s">
-        <v>1338</v>
+        <v>1348</v>
       </c>
       <c r="H165" s="6" t="s">
-        <v>1339</v>
+        <v>1349</v>
       </c>
       <c r="I165" s="6" t="s">
         <v>26</v>
@@ -19199,7 +19282,7 @@
         <v>26</v>
       </c>
       <c r="L165" s="6" t="s">
-        <v>1340</v>
+        <v>1350</v>
       </c>
       <c r="M165" s="6" t="s">
         <v>26</v>
@@ -19211,25 +19294,25 @@
         <v>26</v>
       </c>
       <c r="P165" s="6" t="s">
-        <v>1341</v>
+        <v>1351</v>
       </c>
       <c r="Q165" s="6" t="s">
         <v>26</v>
       </c>
       <c r="R165" s="6" t="s">
-        <v>1342</v>
+        <v>1352</v>
       </c>
       <c r="S165" s="6" t="s">
         <v>26</v>
       </c>
       <c r="T165" s="6" t="s">
-        <v>1343</v>
+        <v>1353</v>
       </c>
       <c r="U165" s="6">
         <v>1</v>
       </c>
       <c r="V165" s="6" t="s">
-        <v>1344</v>
+        <v>1354</v>
       </c>
       <c r="W165" s="6" t="s">
         <v>26</v>
@@ -19243,22 +19326,22 @@
         <v>222</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>1347</v>
+        <v>1357</v>
       </c>
       <c r="I166" s="6" t="s">
         <v>26</v>
@@ -19267,10 +19350,10 @@
         <v>26</v>
       </c>
       <c r="K166" s="6" t="s">
-        <v>1348</v>
+        <v>1358</v>
       </c>
       <c r="L166" s="6" t="s">
-        <v>1349</v>
+        <v>1359</v>
       </c>
       <c r="M166" s="6" t="s">
         <v>26</v>
@@ -19279,10 +19362,10 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>1350</v>
+        <v>1360</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>1351</v>
+        <v>1361</v>
       </c>
       <c r="Q166" s="6" t="s">
         <v>26</v>
@@ -19291,7 +19374,7 @@
         <v>26</v>
       </c>
       <c r="S166" s="6" t="s">
-        <v>1352</v>
+        <v>1362</v>
       </c>
       <c r="T166" s="6" t="s">
         <v>26</v>
@@ -19300,7 +19383,7 @@
         <v>9</v>
       </c>
       <c r="V166" s="6" t="s">
-        <v>1353</v>
+        <v>1363</v>
       </c>
       <c r="W166" s="6" t="s">
         <v>26</v>
@@ -19314,19 +19397,19 @@
         <v>222</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>1354</v>
+        <v>1364</v>
       </c>
       <c r="D167" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F167" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G167" s="6" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="H167" s="6" t="s">
         <v>26</v>
@@ -19385,22 +19468,22 @@
         <v>222</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>1355</v>
+        <v>1365</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>1356</v>
+        <v>1366</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>1357</v>
+        <v>1367</v>
       </c>
       <c r="I168" s="6" t="s">
         <v>26</v>
@@ -19412,19 +19495,19 @@
         <v>26</v>
       </c>
       <c r="L168" s="6" t="s">
-        <v>1358</v>
+        <v>1368</v>
       </c>
       <c r="M168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>1359</v>
+        <v>1369</v>
       </c>
       <c r="O168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>1360</v>
+        <v>1370</v>
       </c>
       <c r="Q168" s="6" t="s">
         <v>26</v>
@@ -19433,7 +19516,7 @@
         <v>26</v>
       </c>
       <c r="S168" s="6" t="s">
-        <v>1361</v>
+        <v>1371</v>
       </c>
       <c r="T168" s="6" t="s">
         <v>26</v>
@@ -19442,7 +19525,7 @@
         <v>11</v>
       </c>
       <c r="V168" s="6" t="s">
-        <v>1362</v>
+        <v>1372</v>
       </c>
       <c r="W168" s="6" t="s">
         <v>26</v>
@@ -19456,22 +19539,22 @@
         <v>222</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>1363</v>
+        <v>1373</v>
       </c>
       <c r="D169" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G169" s="6" t="s">
-        <v>1364</v>
+        <v>1374</v>
       </c>
       <c r="H169" s="6" t="s">
-        <v>1365</v>
+        <v>1375</v>
       </c>
       <c r="I169" s="6" t="s">
         <v>26</v>
@@ -19483,37 +19566,37 @@
         <v>26</v>
       </c>
       <c r="L169" s="6" t="s">
-        <v>1366</v>
+        <v>1376</v>
       </c>
       <c r="M169" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N169" s="6" t="s">
-        <v>1367</v>
+        <v>1377</v>
       </c>
       <c r="O169" s="6" t="s">
-        <v>1368</v>
+        <v>1378</v>
       </c>
       <c r="P169" s="6" t="s">
-        <v>1369</v>
+        <v>1379</v>
       </c>
       <c r="Q169" s="6" t="s">
-        <v>1370</v>
+        <v>1380</v>
       </c>
       <c r="R169" s="6" t="s">
         <v>26</v>
       </c>
       <c r="S169" s="6" t="s">
-        <v>1371</v>
+        <v>1381</v>
       </c>
       <c r="T169" s="6" t="s">
-        <v>1372</v>
+        <v>1382</v>
       </c>
       <c r="U169" s="6">
         <v>12</v>
       </c>
       <c r="V169" s="6" t="s">
-        <v>1373</v>
+        <v>1383</v>
       </c>
       <c r="W169" s="6" t="s">
         <v>26</v>
@@ -19524,25 +19607,25 @@
         <v>168</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>1374</v>
+        <v>1384</v>
       </c>
       <c r="D170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>1376</v>
+        <v>1386</v>
       </c>
       <c r="I170" s="6" t="s">
         <v>26</v>
@@ -19551,10 +19634,10 @@
         <v>26</v>
       </c>
       <c r="K170" s="6" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="L170" s="6" t="s">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="M170" s="6" t="s">
         <v>26</v>
@@ -19563,10 +19646,10 @@
         <v>26</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>1379</v>
+        <v>1389</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>1380</v>
+        <v>1390</v>
       </c>
       <c r="Q170" s="6" t="s">
         <v>26</v>
@@ -19575,7 +19658,7 @@
         <v>26</v>
       </c>
       <c r="S170" s="6" t="s">
-        <v>1381</v>
+        <v>1391</v>
       </c>
       <c r="T170" s="6" t="s">
         <v>26</v>
@@ -19584,7 +19667,7 @@
         <v>9</v>
       </c>
       <c r="V170" s="6" t="s">
-        <v>1382</v>
+        <v>1392</v>
       </c>
       <c r="W170" s="6" t="s">
         <v>26</v>
@@ -19595,37 +19678,37 @@
         <v>169</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>1383</v>
+        <v>1393</v>
       </c>
       <c r="D171" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G171" s="6" t="s">
-        <v>1384</v>
+        <v>1394</v>
       </c>
       <c r="H171" s="6" t="s">
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="I171" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J171" s="6" t="s">
-        <v>1386</v>
+        <v>1396</v>
       </c>
       <c r="K171" s="6" t="s">
-        <v>1387</v>
+        <v>1397</v>
       </c>
       <c r="L171" s="6" t="s">
-        <v>1388</v>
+        <v>1398</v>
       </c>
       <c r="M171" s="6" t="s">
         <v>26</v>
@@ -19634,10 +19717,10 @@
         <v>26</v>
       </c>
       <c r="O171" s="6" t="s">
-        <v>1389</v>
+        <v>1399</v>
       </c>
       <c r="P171" s="6" t="s">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="Q171" s="6" t="s">
         <v>26</v>
@@ -19655,7 +19738,7 @@
         <v>7</v>
       </c>
       <c r="V171" s="6" t="s">
-        <v>1391</v>
+        <v>1401</v>
       </c>
       <c r="W171" s="6" t="s">
         <v>26</v>
@@ -19666,25 +19749,25 @@
         <v>170</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>1392</v>
+        <v>1402</v>
       </c>
       <c r="D172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>1393</v>
+        <v>1403</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>1394</v>
+        <v>1404</v>
       </c>
       <c r="I172" s="6" t="s">
         <v>26</v>
@@ -19696,37 +19779,37 @@
         <v>26</v>
       </c>
       <c r="L172" s="6" t="s">
-        <v>1395</v>
+        <v>1405</v>
       </c>
       <c r="M172" s="6" t="s">
-        <v>1396</v>
+        <v>1406</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>1397</v>
+        <v>1407</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>1398</v>
+        <v>1408</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>1399</v>
+        <v>1409</v>
       </c>
       <c r="Q172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="R172" s="6" t="s">
-        <v>1400</v>
+        <v>1410</v>
       </c>
       <c r="S172" s="6" t="s">
-        <v>1401</v>
+        <v>1411</v>
       </c>
       <c r="T172" s="6" t="s">
-        <v>1402</v>
+        <v>1412</v>
       </c>
       <c r="U172" s="6">
         <v>10</v>
       </c>
       <c r="V172" s="6" t="s">
-        <v>1403</v>
+        <v>1413</v>
       </c>
       <c r="W172" s="6" t="s">
         <v>26</v>
@@ -19737,37 +19820,37 @@
         <v>171</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>1404</v>
+        <v>1414</v>
       </c>
       <c r="D173" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F173" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G173" s="6" t="s">
-        <v>1244</v>
+        <v>1253</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>1405</v>
+        <v>1415</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>1406</v>
+        <v>1416</v>
       </c>
       <c r="J173" s="6" t="s">
-        <v>1407</v>
+        <v>1417</v>
       </c>
       <c r="K173" s="6" t="s">
-        <v>1408</v>
+        <v>1418</v>
       </c>
       <c r="L173" s="6" t="s">
-        <v>1409</v>
+        <v>1419</v>
       </c>
       <c r="M173" s="6" t="s">
         <v>26</v>
@@ -19776,10 +19859,10 @@
         <v>26</v>
       </c>
       <c r="O173" s="6" t="s">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="P173" s="6" t="s">
-        <v>1411</v>
+        <v>1421</v>
       </c>
       <c r="Q173" s="6" t="s">
         <v>26</v>
@@ -19788,7 +19871,7 @@
         <v>26</v>
       </c>
       <c r="S173" s="6" t="s">
-        <v>1412</v>
+        <v>1422</v>
       </c>
       <c r="T173" s="6" t="s">
         <v>26</v>
@@ -19797,7 +19880,7 @@
         <v>7</v>
       </c>
       <c r="V173" s="6" t="s">
-        <v>1413</v>
+        <v>1423</v>
       </c>
       <c r="W173" s="6" t="s">
         <v>26</v>
@@ -19811,46 +19894,46 @@
         <v>239</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>1414</v>
+        <v>1424</v>
       </c>
       <c r="D174" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>1415</v>
+        <v>1425</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>1416</v>
+        <v>1426</v>
       </c>
       <c r="I174" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J174" s="6" t="s">
-        <v>1417</v>
+        <v>1427</v>
       </c>
       <c r="K174" s="6" t="s">
-        <v>1418</v>
+        <v>1428</v>
       </c>
       <c r="L174" s="6" t="s">
-        <v>1419</v>
+        <v>1429</v>
       </c>
       <c r="M174" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>1420</v>
+        <v>1430</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>1421</v>
+        <v>1431</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="Q174" s="6" t="s">
         <v>26</v>
@@ -19868,7 +19951,7 @@
         <v>5</v>
       </c>
       <c r="V174" s="6" t="s">
-        <v>1423</v>
+        <v>1433</v>
       </c>
       <c r="W174" s="6" t="s">
         <v>26</v>
@@ -19882,22 +19965,22 @@
         <v>239</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>1424</v>
+        <v>1434</v>
       </c>
       <c r="D175" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F175" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G175" s="6" t="s">
-        <v>1425</v>
+        <v>1435</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>1426</v>
+        <v>1436</v>
       </c>
       <c r="I175" s="6" t="s">
         <v>26</v>
@@ -19906,10 +19989,10 @@
         <v>26</v>
       </c>
       <c r="K175" s="6" t="s">
-        <v>1427</v>
+        <v>1437</v>
       </c>
       <c r="L175" s="6" t="s">
-        <v>1428</v>
+        <v>1438</v>
       </c>
       <c r="M175" s="6" t="s">
         <v>26</v>
@@ -19921,7 +20004,7 @@
         <v>26</v>
       </c>
       <c r="P175" s="6" t="s">
-        <v>1429</v>
+        <v>1439</v>
       </c>
       <c r="Q175" s="6" t="s">
         <v>26</v>
@@ -19930,7 +20013,7 @@
         <v>26</v>
       </c>
       <c r="S175" s="6" t="s">
-        <v>1430</v>
+        <v>1440</v>
       </c>
       <c r="T175" s="6" t="s">
         <v>26</v>
@@ -19939,7 +20022,7 @@
         <v>10</v>
       </c>
       <c r="V175" s="6" t="s">
-        <v>1431</v>
+        <v>1441</v>
       </c>
       <c r="W175" s="6" t="s">
         <v>26</v>
@@ -19953,34 +20036,34 @@
         <v>239</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>1432</v>
+        <v>1442</v>
       </c>
       <c r="D176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>1332</v>
+        <v>1342</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>1433</v>
+        <v>1443</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>1434</v>
+        <v>1444</v>
       </c>
       <c r="J176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="K176" s="6" t="s">
-        <v>1435</v>
+        <v>1445</v>
       </c>
       <c r="L176" s="6" t="s">
-        <v>1436</v>
+        <v>1446</v>
       </c>
       <c r="M176" s="6" t="s">
         <v>26</v>
@@ -19992,7 +20075,7 @@
         <v>26</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>1437</v>
+        <v>1447</v>
       </c>
       <c r="Q176" s="6" t="s">
         <v>26</v>
@@ -20001,16 +20084,16 @@
         <v>26</v>
       </c>
       <c r="S176" s="6" t="s">
-        <v>1438</v>
+        <v>1448</v>
       </c>
       <c r="T176" s="6" t="s">
-        <v>1439</v>
+        <v>1449</v>
       </c>
       <c r="U176" s="6">
         <v>4</v>
       </c>
       <c r="V176" s="6" t="s">
-        <v>1440</v>
+        <v>1450</v>
       </c>
       <c r="W176" s="6" t="s">
         <v>26</v>
@@ -20024,22 +20107,22 @@
         <v>239</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>1441</v>
+        <v>1451</v>
       </c>
       <c r="D177" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G177" s="6" t="s">
-        <v>1442</v>
+        <v>1452</v>
       </c>
       <c r="H177" s="6" t="s">
-        <v>1443</v>
+        <v>1453</v>
       </c>
       <c r="I177" s="6" t="s">
         <v>26</v>
@@ -20048,22 +20131,22 @@
         <v>26</v>
       </c>
       <c r="K177" s="6" t="s">
-        <v>1444</v>
+        <v>1454</v>
       </c>
       <c r="L177" s="6" t="s">
-        <v>1445</v>
+        <v>1455</v>
       </c>
       <c r="M177" s="6" t="s">
-        <v>1446</v>
+        <v>1456</v>
       </c>
       <c r="N177" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O177" s="6" t="s">
-        <v>1447</v>
+        <v>1457</v>
       </c>
       <c r="P177" s="6" t="s">
-        <v>1448</v>
+        <v>1458</v>
       </c>
       <c r="Q177" s="6" t="s">
         <v>26</v>
@@ -20072,16 +20155,16 @@
         <v>26</v>
       </c>
       <c r="S177" s="6" t="s">
-        <v>1449</v>
+        <v>1459</v>
       </c>
       <c r="T177" s="6" t="s">
-        <v>1444</v>
+        <v>1454</v>
       </c>
       <c r="U177" s="6">
         <v>1</v>
       </c>
       <c r="V177" s="6" t="s">
-        <v>1450</v>
+        <v>1460</v>
       </c>
       <c r="W177" s="6" t="s">
         <v>26</v>
@@ -20095,34 +20178,34 @@
         <v>239</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>1451</v>
+        <v>1461</v>
       </c>
       <c r="D178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>1452</v>
+        <v>1462</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>1453</v>
+        <v>1463</v>
       </c>
       <c r="I178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J178" s="6" t="s">
-        <v>1454</v>
+        <v>1464</v>
       </c>
       <c r="K178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="L178" s="6" t="s">
-        <v>1455</v>
+        <v>1465</v>
       </c>
       <c r="M178" s="6" t="s">
         <v>26</v>
@@ -20131,16 +20214,16 @@
         <v>26</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>1456</v>
+        <v>1466</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>1457</v>
+        <v>1467</v>
       </c>
       <c r="Q178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="R178" s="6" t="s">
-        <v>1458</v>
+        <v>1468</v>
       </c>
       <c r="S178" s="6" t="s">
         <v>26</v>
@@ -20152,7 +20235,7 @@
         <v>5</v>
       </c>
       <c r="V178" s="6" t="s">
-        <v>1459</v>
+        <v>1469</v>
       </c>
       <c r="W178" s="6" t="s">
         <v>26</v>
@@ -20166,34 +20249,34 @@
         <v>239</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>1460</v>
+        <v>1470</v>
       </c>
       <c r="D179" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F179" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G179" s="6" t="s">
-        <v>1461</v>
+        <v>1471</v>
       </c>
       <c r="H179" s="6" t="s">
-        <v>1462</v>
+        <v>1472</v>
       </c>
       <c r="I179" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J179" s="6" t="s">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="K179" s="6" t="s">
-        <v>1464</v>
+        <v>1474</v>
       </c>
       <c r="L179" s="6" t="s">
-        <v>1465</v>
+        <v>1475</v>
       </c>
       <c r="M179" s="6" t="s">
         <v>26</v>
@@ -20202,10 +20285,10 @@
         <v>26</v>
       </c>
       <c r="O179" s="6" t="s">
-        <v>1466</v>
+        <v>1476</v>
       </c>
       <c r="P179" s="6" t="s">
-        <v>1467</v>
+        <v>1477</v>
       </c>
       <c r="Q179" s="6" t="s">
         <v>26</v>
@@ -20217,13 +20300,13 @@
         <v>26</v>
       </c>
       <c r="T179" s="6" t="s">
-        <v>1466</v>
+        <v>1476</v>
       </c>
       <c r="U179" s="6">
         <v>7</v>
       </c>
       <c r="V179" s="6" t="s">
-        <v>1468</v>
+        <v>1478</v>
       </c>
       <c r="W179" s="6" t="s">
         <v>26</v>
@@ -20237,22 +20320,22 @@
         <v>239</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>1469</v>
+        <v>1479</v>
       </c>
       <c r="D180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>1470</v>
+        <v>1480</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>1471</v>
+        <v>1481</v>
       </c>
       <c r="I180" s="6" t="s">
         <v>26</v>
@@ -20264,7 +20347,7 @@
         <v>26</v>
       </c>
       <c r="L180" s="6" t="s">
-        <v>1472</v>
+        <v>1482</v>
       </c>
       <c r="M180" s="6" t="s">
         <v>26</v>
@@ -20276,7 +20359,7 @@
         <v>26</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>1473</v>
+        <v>1483</v>
       </c>
       <c r="Q180" s="6" t="s">
         <v>26</v>
@@ -20294,7 +20377,7 @@
         <v>16</v>
       </c>
       <c r="V180" s="6" t="s">
-        <v>1474</v>
+        <v>1484</v>
       </c>
       <c r="W180" s="6" t="s">
         <v>26</v>
@@ -20308,22 +20391,22 @@
         <v>245</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>1475</v>
+        <v>1485</v>
       </c>
       <c r="D181" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F181" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G181" s="6" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>1476</v>
+        <v>1486</v>
       </c>
       <c r="I181" s="6" t="s">
         <v>26</v>
@@ -20332,10 +20415,10 @@
         <v>26</v>
       </c>
       <c r="K181" s="6" t="s">
-        <v>1477</v>
+        <v>1487</v>
       </c>
       <c r="L181" s="6" t="s">
-        <v>1478</v>
+        <v>1488</v>
       </c>
       <c r="M181" s="6" t="s">
         <v>26</v>
@@ -20365,7 +20448,7 @@
         <v>12</v>
       </c>
       <c r="V181" s="6" t="s">
-        <v>1479</v>
+        <v>1489</v>
       </c>
       <c r="W181" s="6" t="s">
         <v>26</v>
@@ -20379,46 +20462,46 @@
         <v>245</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>1480</v>
+        <v>1490</v>
       </c>
       <c r="D182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>1481</v>
+        <v>1491</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>1482</v>
+        <v>1492</v>
       </c>
       <c r="I182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J182" s="6" t="s">
-        <v>1483</v>
+        <v>1493</v>
       </c>
       <c r="K182" s="6" t="s">
-        <v>1484</v>
+        <v>1494</v>
       </c>
       <c r="L182" s="6" t="s">
-        <v>1485</v>
+        <v>1495</v>
       </c>
       <c r="M182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>1486</v>
+        <v>1496</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="Q182" s="6" t="s">
         <v>26</v>
@@ -20436,7 +20519,7 @@
         <v>13</v>
       </c>
       <c r="V182" s="6" t="s">
-        <v>1489</v>
+        <v>1499</v>
       </c>
       <c r="W182" s="6" t="s">
         <v>26</v>
@@ -20450,22 +20533,22 @@
         <v>264</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>1490</v>
+        <v>1500</v>
       </c>
       <c r="D183" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F183" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G183" s="6" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>1491</v>
+        <v>1501</v>
       </c>
       <c r="I183" s="6" t="s">
         <v>26</v>
@@ -20477,16 +20560,16 @@
         <v>26</v>
       </c>
       <c r="L183" s="6" t="s">
-        <v>1492</v>
+        <v>1502</v>
       </c>
       <c r="M183" s="6" t="s">
-        <v>1493</v>
+        <v>1503</v>
       </c>
       <c r="N183" s="6" t="s">
-        <v>1494</v>
+        <v>1504</v>
       </c>
       <c r="O183" s="6" t="s">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="P183" s="6" t="s">
         <v>26</v>
@@ -20507,7 +20590,7 @@
         <v>15</v>
       </c>
       <c r="V183" s="6" t="s">
-        <v>1496</v>
+        <v>1506</v>
       </c>
       <c r="W183" s="6" t="s">
         <v>26</v>
@@ -20521,22 +20604,22 @@
         <v>296</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>1497</v>
+        <v>1507</v>
       </c>
       <c r="D184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>1498</v>
+        <v>1508</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>1499</v>
+        <v>1509</v>
       </c>
       <c r="I184" s="6" t="s">
         <v>26</v>
@@ -20545,10 +20628,10 @@
         <v>26</v>
       </c>
       <c r="K184" s="6" t="s">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="L184" s="6" t="s">
-        <v>1501</v>
+        <v>1511</v>
       </c>
       <c r="M184" s="6" t="s">
         <v>26</v>
@@ -20557,10 +20640,10 @@
         <v>26</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>1502</v>
+        <v>1512</v>
       </c>
       <c r="Q184" s="6" t="s">
         <v>26</v>
@@ -20569,16 +20652,16 @@
         <v>26</v>
       </c>
       <c r="S184" s="6" t="s">
-        <v>1503</v>
+        <v>1513</v>
       </c>
       <c r="T184" s="6" t="s">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="U184" s="6">
         <v>12</v>
       </c>
       <c r="V184" s="6" t="s">
-        <v>1504</v>
+        <v>1514</v>
       </c>
       <c r="W184" s="6" t="s">
         <v>26</v>
@@ -20592,19 +20675,19 @@
         <v>296</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>1505</v>
+        <v>1515</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F185" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G185" s="6" t="s">
-        <v>1506</v>
+        <v>1516</v>
       </c>
       <c r="H185" s="6" t="s">
         <v>26</v>
@@ -20649,7 +20732,7 @@
         <v>12</v>
       </c>
       <c r="V185" s="6" t="s">
-        <v>1507</v>
+        <v>1517</v>
       </c>
       <c r="W185" s="6" t="s">
         <v>26</v>
@@ -20663,37 +20746,37 @@
         <v>296</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>1508</v>
+        <v>1518</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>1509</v>
+        <v>1519</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>1511</v>
+        <v>1521</v>
       </c>
       <c r="J186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="K186" s="6" t="s">
-        <v>1512</v>
+        <v>1522</v>
       </c>
       <c r="L186" s="6" t="s">
-        <v>1513</v>
+        <v>1523</v>
       </c>
       <c r="M186" s="6" t="s">
-        <v>1514</v>
+        <v>1524</v>
       </c>
       <c r="N186" s="6" t="s">
         <v>26</v>
@@ -20702,7 +20785,7 @@
         <v>26</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>1515</v>
+        <v>1525</v>
       </c>
       <c r="Q186" s="6" t="s">
         <v>26</v>
@@ -20711,7 +20794,7 @@
         <v>26</v>
       </c>
       <c r="S186" s="6" t="s">
-        <v>1516</v>
+        <v>1526</v>
       </c>
       <c r="T186" s="6" t="s">
         <v>26</v>
@@ -20720,7 +20803,7 @@
         <v>6</v>
       </c>
       <c r="V186" s="6" t="s">
-        <v>1517</v>
+        <v>1527</v>
       </c>
       <c r="W186" s="6" t="s">
         <v>26</v>
@@ -20734,22 +20817,22 @@
         <v>333</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>1518</v>
+        <v>1528</v>
       </c>
       <c r="D187" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F187" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G187" s="6" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="I187" s="6" t="s">
         <v>26</v>
@@ -20761,19 +20844,19 @@
         <v>26</v>
       </c>
       <c r="L187" s="6" t="s">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="M187" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N187" s="6" t="s">
-        <v>1521</v>
+        <v>1531</v>
       </c>
       <c r="O187" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P187" s="6" t="s">
-        <v>1522</v>
+        <v>1532</v>
       </c>
       <c r="Q187" s="6" t="s">
         <v>26</v>
@@ -20791,7 +20874,7 @@
         <v>5</v>
       </c>
       <c r="V187" s="6" t="s">
-        <v>1523</v>
+        <v>1533</v>
       </c>
       <c r="W187" s="6" t="s">
         <v>26</v>
@@ -20805,64 +20888,64 @@
         <v>341</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>1524</v>
+        <v>1534</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>1525</v>
+        <v>1535</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>1526</v>
+        <v>1536</v>
       </c>
       <c r="I188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J188" s="6" t="s">
-        <v>1527</v>
+        <v>1537</v>
       </c>
       <c r="K188" s="6" t="s">
-        <v>1528</v>
+        <v>1538</v>
       </c>
       <c r="L188" s="6" t="s">
-        <v>1529</v>
+        <v>1539</v>
       </c>
       <c r="M188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>1530</v>
+        <v>1540</v>
       </c>
       <c r="O188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>1531</v>
+        <v>1541</v>
       </c>
       <c r="Q188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="R188" s="6" t="s">
-        <v>1532</v>
+        <v>1542</v>
       </c>
       <c r="S188" s="6" t="s">
-        <v>1533</v>
+        <v>1543</v>
       </c>
       <c r="T188" s="6" t="s">
-        <v>1534</v>
+        <v>1544</v>
       </c>
       <c r="U188" s="6">
         <v>14</v>
       </c>
       <c r="V188" s="6" t="s">
-        <v>1535</v>
+        <v>1545</v>
       </c>
       <c r="W188" s="6" t="s">
         <v>26</v>
@@ -20876,34 +20959,34 @@
         <v>341</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>1536</v>
+        <v>1546</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F189" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G189" s="6" t="s">
-        <v>1537</v>
+        <v>1547</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>1538</v>
+        <v>1548</v>
       </c>
       <c r="I189" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J189" s="6" t="s">
-        <v>1539</v>
+        <v>1549</v>
       </c>
       <c r="K189" s="6" t="s">
-        <v>1540</v>
+        <v>1550</v>
       </c>
       <c r="L189" s="6" t="s">
-        <v>1541</v>
+        <v>1551</v>
       </c>
       <c r="M189" s="6" t="s">
         <v>26</v>
@@ -20915,25 +20998,25 @@
         <v>26</v>
       </c>
       <c r="P189" s="6" t="s">
-        <v>1542</v>
+        <v>1552</v>
       </c>
       <c r="Q189" s="6" t="s">
         <v>26</v>
       </c>
       <c r="R189" s="6" t="s">
-        <v>1543</v>
+        <v>1553</v>
       </c>
       <c r="S189" s="6" t="s">
-        <v>1544</v>
+        <v>1554</v>
       </c>
       <c r="T189" s="6" t="s">
-        <v>1545</v>
+        <v>1555</v>
       </c>
       <c r="U189" s="6">
         <v>11</v>
       </c>
       <c r="V189" s="6" t="s">
-        <v>1546</v>
+        <v>1556</v>
       </c>
       <c r="W189" s="6" t="s">
         <v>26</v>
@@ -20947,22 +21030,22 @@
         <v>341</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>1547</v>
+        <v>1557</v>
       </c>
       <c r="D190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>1548</v>
+        <v>1558</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>1549</v>
+        <v>1559</v>
       </c>
       <c r="I190" s="6" t="s">
         <v>26</v>
@@ -20971,40 +21054,40 @@
         <v>26</v>
       </c>
       <c r="K190" s="6" t="s">
-        <v>1550</v>
+        <v>1560</v>
       </c>
       <c r="L190" s="6" t="s">
-        <v>1551</v>
+        <v>1561</v>
       </c>
       <c r="M190" s="6" t="s">
-        <v>1552</v>
+        <v>1562</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>1553</v>
+        <v>1563</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>1554</v>
+        <v>1564</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>1555</v>
+        <v>1565</v>
       </c>
       <c r="Q190" s="6" t="s">
-        <v>1556</v>
+        <v>1566</v>
       </c>
       <c r="R190" s="6" t="s">
-        <v>1557</v>
+        <v>1567</v>
       </c>
       <c r="S190" s="6" t="s">
-        <v>1558</v>
+        <v>1568</v>
       </c>
       <c r="T190" s="6" t="s">
-        <v>1559</v>
+        <v>1569</v>
       </c>
       <c r="U190" s="6">
         <v>10</v>
       </c>
       <c r="V190" s="6" t="s">
-        <v>1560</v>
+        <v>1570</v>
       </c>
       <c r="W190" s="6" t="s">
         <v>26</v>

--- a/dataset/全国重点院校/全国高校汇总表.xlsx
+++ b/dataset/全国重点院校/全国高校汇总表.xlsx
@@ -201,8 +201,7 @@
 智能交互学院 | https://sii.ecnu.edu.cn/ | 电话:009102000042
 上海国际首席技术官学院 | https://cto.ecnu.edu.cn/main.htm | 电话:021-61911352
 精密光谱科学与技术高等研究院 | http://www.lps.ecnu.edu.cn/ | 邮箱:lps@phy.ecnu.edu.cn | 电话:021-54836023
-量子科学与精密测量研究院 | https://iqspm.ecnu.edu.cn/index.html?_refluxos=a10https://iqspm.ecnu.edu.cn/index.html?_refluxos=a10 | 邮箱:jtsheng@lps.ecnu.edu.cn | 电话:(86)21-54836079
-地理科学学院 | http://www.geo.ecnu.edu.cn/ | 邮箱:ghwang@geo.ec; geo@geo.ecnu.edu.cn | 电话:54341218</t>
+量子科学与精密测量研究院 | https://iqspm.ecnu.edu.cn/index.html?_refluxos=a10https://iqspm.ecnu.edu.cn/index.html?_refluxos=a10 | 邮箱:jtsheng@lps.ecnu.edu.cn | 电话:(86)21-54836079</t>
   </si>
   <si>
     <t>同济大学</t>
@@ -300,7 +299,7 @@
     <t>数学科学学院 | http://math.fudan.edu.cn/ | 邮箱:sxbks@fudan.edu.cn | 电话:021-65642222; 55665146）; 65643503）
 微电子学院 | https://sme.fudan.edu.cn/ | 邮箱:sme_keyan@fudan.edu.cn; sme_admission@fudan.edu.cn; sme@fudan.edu.cn | 电话:021-65641106; 021-65643449; 021-65643438
 生命科学学院 | http://life.fudan.edu.cn/ | 电话:08660525549
-大数据学院 | http://www.sds.fudan.edu.cn/wp/
+大数据学院 | https://sds.fudan.edu.cn/
 集成电路与微纳电子创新学院 | https://icmne.fudan.edu.cn/ | 邮箱:icmne@fudan.edu.cn
 计算与智能创新学院 | https://ai.fudan.edu.cn/ | 邮箱:cs_school@fudan.edu.cn | 电话:13472188450
 智能机器人与先进制造创新学院 | https://ciram.fudan.edu.cn/ | 邮箱:ciram_dzb@fudan.edu.cn; yingsun@fudan.edu.cn; teai@fudan.edu.cn | 电话:021-65641208; 021-31243536; 021-65642740
@@ -324,18 +323,18 @@
     <t>https://pgs.ruc.edu.cn/gats.htm</t>
   </si>
   <si>
-    <t>■ 生态环境学院 | https://envi.ruc.edu.cn/ | 邮箱:huanjing@ruc.edu.cn | 电话:010-62511042
-■ 信息学院 | http://info.ruc.edu.cn/
-■ 统计学院 | http://stat.ruc.edu.cn/ | 邮箱:tongjioffice@ruc.edu.cn | 电话:01620241114; 010-62511318; 010-62511316
-■ 化学与生命资源学院 | https://clr.ruc.edu.cn/zwwz/index.htm | 邮箱:ruc_clr@ruc.edu.cn | 电话:010-62512822
-■ 物理学院 | http://www.phys.ruc.edu.cn/ | 邮箱:graphy@ruc.edu.cn | 电话:+86-10-62517997（
-■ 统计与大数据研究院 | http://isbd.ruc.edu.cn/
-■ 数学学院 | http://math.ruc.edu.cn/ | 邮箱:mathruc@ruc.edu.cn | 电话:010-82507161
-■ 高瓴人工智能学院 | http://ai.ruc.edu.cn/ | 邮箱:ai@ruc.edu.cn
-■ 智慧治理学院 | http://su.ruc.edu.cn/department/ssg/index.htm | 电话:045931565425
+    <t>生态环境学院 | https://envi.ruc.edu.cn/ | 邮箱:huanjing@ruc.edu.cn | 电话:010-62511042
+信息学院 | http://info.ruc.edu.cn/
+统计学院 | http://stat.ruc.edu.cn/ | 邮箱:tongjioffice@ruc.edu.cn | 电话:01620241114; 010-62511318; 010-62511316
+化学与生命资源学院 | https://clr.ruc.edu.cn/zwwz/index.htm | 邮箱:ruc_clr@ruc.edu.cn | 电话:010-62512822
+物理学院 | http://www.phys.ruc.edu.cn/ | 邮箱:graphy@ruc.edu.cn | 电话:+86-10-62517997（
+统计与大数据研究院 | http://isbd.ruc.edu.cn/
+数学学院 | http://math.ruc.edu.cn/ | 邮箱:mathruc@ruc.edu.cn | 电话:010-82507161
+高瓴人工智能学院 | http://ai.ruc.edu.cn/ | 邮箱:ai@ruc.edu.cn
+智慧治理学院 | http://su.ruc.edu.cn/department/ssg/index.htm | 电话:045931565425
 国家治理工程学院 | http://ang.ruc.edu.cn/index.htm | 邮箱:GJZL@ruc.edu.cn | 电话:010-62510553
-■ 全球领导力学院 | http://sgl.ruc.edu.cn/ | 邮箱:sglruc@ruc.edu.cn
-■ 交叉科学研究院 | http://sids.ruc.edu.cn/ | 邮箱:rdcy2021@ruc.edu.cn | 电话:010-62510183</t>
+全球领导力学院 | http://sgl.ruc.edu.cn/ | 邮箱:sglruc@ruc.edu.cn
+交叉科学研究院 | http://sids.ruc.edu.cn/ | 邮箱:rdcy2021@ruc.edu.cn | 电话:010-62510183</t>
   </si>
   <si>
     <t>中国农业大学</t>
@@ -615,8 +614,7 @@
 交叉信息研究院 | https://iiis.tsinghua.edu.cn/ | 邮箱:iiis@mail.tsinghua.edu.cn | 电话:010-62781693
 航空发动机研究院 | http://www.ae.tsinghua.edu.cn/ | 邮箱:hfyzhb@mailoa.tsinghua.edu.cn; hfykyb@tsinghua.edu.cn | 电话:62796693; 62786853; 62771763
 智能产业研究院 | https://air.tsinghua.edu.cn/ | 邮箱:airoffice@air.tsinghua.edu.cn; airhr@air.tsinghua.edu.cn | 电话:(010)82151160
-国家卓越工程师学院 | https://www.ngce.tsinghua.edu.cn/ | 邮箱:gcsxy@tsinghua.edu.cn | 电话:010-62793784
-人工智能学院 | http://collegeai.tsinghua.edu.cn/ | 邮箱:collegeai@mail.tsinghua.edu.cn | 电话:62788817</t>
+国家卓越工程师学院 | https://www.ngce.tsinghua.edu.cn/ | 邮箱:gcsxy@tsinghua.edu.cn | 电话:010-62793784</t>
   </si>
   <si>
     <t>吉林省</t>
@@ -1316,26 +1314,26 @@
     <t>科学技术研究院 | http://rd.zju.edu.cn/
 技术转化研究院 | http://www.itt.zju.edu.cn/ | 邮箱:lwu@zju.edu.cn; quxiaodi@zju.edu.cn; ltm@zju.edu.cn | 电话:0571-88982935
 数学科学学院
-物理学院
+物理学院 | https://physics.zju.edu.cn/
 地球科学学院
-机械工程学院
-材料科学与工程学院
+机械工程学院 | http://me.zju.edu.cn/
+材料科学与工程学院 | https://mse.zju.edu.cn/
 能源工程学院
-电气工程学院
+电气工程学院 | http://ee.zju.edu.cn/
 建筑工程学院
-化学工程与生物工程学院
-海洋学院
-航空航天学院
-光电科学与工程学院
+化学工程与生物工程学院 | http://che.zju.edu.cn/
+海洋学院 | http://oc.zju.edu.cn/
+航空航天学院 | http://saa.zju.edu.cn/
+光电科学与工程学院 | http://opt.zju.edu.cn/
 信息与电子工程学院
-控制科学与工程学院
+控制科学与工程学院 | http://cse.zju.edu.cn/
 计算机科学与技术学院 —网络空间安全学院
 计算机科学与技术学院
-—网络空间安全学院
+网络空间安全学院
 软件学院
 生物医学工程与仪器科学学院
-集成电路学院
-人工智能学院
+集成电路学院 | https://ic.zju.edu.cn/
+人工智能学院 | https://ai.zju.edu.cn/
 生命科学学院
 生物系统工程与食品科学学院
 环境与资源学院
@@ -1750,7 +1748,7 @@
 材料科学与工程学院 | http://mse.dlut.edu.cn | 邮箱:mse@dlut.edu.cn | 电话:0411-84708430
 能源与动力学院 | http://power.dlut.edu.cn | 邮箱:powere@dlut.edu.cn | 电话:0411-84708460
 电子信息与电气工程学部 | http://ee.dlut.edu.cn/ | 邮箱:dutee@dlut.edu.cn | 电话:0411-84706936
-电气工程学院 | http://eee.dlut.edu.cn
+电气工程学院 | https://ee.dlut.edu.cn/
 信息与通信工程学院 | http://ice.dlut.edu.cn | 邮箱:bowang@dlut.edu.cn
 控制科学与工程学院 | http://scse.dlut.edu.cn | 邮箱:cse@dlut.edu.cn | 电话:0411-84701537
 计算机科学与技术学院 | http://cs.dlut.edu.cn
@@ -2212,8 +2210,7 @@
   </si>
   <si>
     <t>华东化工学院 | https://www.ecust.edu.cn/847/list.htm | 电话:009102000037
-上海化工学院 | https://www.ecust.edu.cn/shhgxy/list.htm | 电话:009102000037
-华东化工学院 | https://www.ecust.edu.cn/709/list.htm | 电话:009102000037</t>
+上海化工学院 | https://www.ecust.edu.cn/shhgxy/list.htm | 电话:009102000037</t>
   </si>
   <si>
     <t>第二军医大学</t>
@@ -2431,13 +2428,7 @@
 人工智能学院 | https://ai.cumtb.edu.cn/ | 邮箱:rgznxy@cumtb.edu.cn | 电话:010-62339761
 力学与土木工程学院 | http://ljxy.cumtb.edu.cn/
 理学院 | http://lxy.cumtb.edu.cn/
-中国矿业大学（北京）内蒙古研究院 | https://nmgyjy.cumtb.edu.cn/ | 电话:17854205908
-能源与矿业学院 | https://nyxy.cumtb.edu.cn
-地球科学与测绘工程学院 | https://dcxy.cumtb.edu.cn/ | 邮箱:yzxxdcxy@163.com | 电话:010-62339300
-化学与环境工程学院 | https://scee.cumtb.edu.cn/
-机械与电气工程学院 | https://jdxy.cumtb.edu.cn/ | 邮箱:jdxy@cumtb.edu.cn | 电话:010-62331370
-力学与土木工程学院 | https://ljxy.cumtb.edu.cn/
-理学院 | https://lxy.cumtb.edu.cn/</t>
+中国矿业大学（北京）内蒙古研究院 | https://nmgyjy.cumtb.edu.cn/ | 电话:17854205908</t>
   </si>
   <si>
     <t>中央财经大学</t>
@@ -2759,8 +2750,7 @@
 工程技术研究院 | http://iet.ustb.edu.cn/ | 邮箱:bkdgyy@ustb.edu.cn | 电话:010-62332598
 大安全科学研究院 | https://mss.ustb.edu.cn/ | 电话:010-62333808
 城镇化与城市安全研究院 | https://iuus.ustb.edu.cn | 电话:010-62334196
-科学技术研究院 | https://research.ustb.edu.cn/ | 电话:0402430062
-资源与安全工程学院 | http://cres.ustb.edu.cn/</t>
+科学技术研究院 | https://research.ustb.edu.cn/ | 电话:0402430062</t>
   </si>
   <si>
     <t>北京邮电大学</t>
@@ -3954,22 +3944,6 @@
 环境科学与工程学院 | http://sese.hainanu.edu.cn | 电话:0898-66255157
 食品科学与工程学院 | https://hd.hainanu.edu.cn/shipin/
 海洋生物与水产学院 | http://smbf.hainanu.edu.cn | 邮箱:xiesg@hainanu.edu.cn; 993928@hainanu.edu.cn; haiyyb@hainu.edu.cn | 电话:0898-66279184
-空天智能学院 | https://sai.hainanu.edu.cn/ | 邮箱:ktzn@hainanu.edu.cn | 电话:0898-66268297
-数学与统计学院 | http://sms.hainanu.edu.cn | 邮箱:hdsxtj@hainanu.edu.cn
-物理与光电工程学院 | http://spoe.hainanu.edu.cn | 邮箱:wdxyzh@hainanu.edu.cn | 电话:0898-66279161
-化学化工学院 | http://scce.hainanu.edu.cn | 邮箱:hdhg@hainanu.edu.cn | 电话:0898-66255906; 0898-66256050; 0898-66279224
-生命健康学院 | http://slhs.hainanu.edu.cn | 邮箱:hdsmkx@hainanu.edu.cn | 电话:0898-66253203（
-机电工程学院 | http://smee.hainanu.edu.cn | 电话:0898-66267576; 0898-66271526; 0898-66267372
-材料科学与工程学院 | http://mse.hainanu.edu.cn | 邮箱:clxyzhb@hainanu.edu.cn | 电话:0898-66251982（
-电子科学与技术学院 | https://hd.hainanu.edu.cn/dzkx/
-信息与通信工程学院 | http://sice.hainanu.edu.cn | 邮箱:sice@hainan.edu.cn | 电话:0898-66279057
-计算机科学与技术学院 | http://cs.hainanu.edu.cn | 邮箱:cs@hainanu.edu.cn | 电话:0898-66278203
-网络空间安全学院 | https://scs.hainanu.edu.cn/ | 邮箱:scscs@hainanu.edu.cn | 电话:0898-66259127; 0898-66257132
-土木建筑工程学院 | http://scea.hainanu.edu.cn | 电话:0898-66279232
-海洋技术与装备学院 | http://smse.hainanu.edu.cn/ | 邮箱:sheny2000@hainanu.edu.cn; 991302@hainanu.edu.cn | 电话:0898-66192572; 0898-66255276
-环境科学与工程学院 | http://sese.hainanu.edu.cn | 电话:0898-66255157
-食品科学与工程学院 | https://hd.hainanu.edu.cn/shipin/
-海洋生物与水产学院 | http://smbf.hainanu.edu.cn | 邮箱:xiesg@hainanu.edu.cn; 993928@hainanu.edu.cn; haiyyb@hainu.edu.cn | 电话:0898-66279184
 空天智能学院 | https://sai.hainanu.edu.cn/ | 邮箱:ktzn@hainanu.edu.cn | 电话:0898-66268297</t>
   </si>
   <si>
@@ -4122,13 +4096,13 @@
 等共计 助理</t>
   </si>
   <si>
-    <t>◆ 心理学院 | http://psych.ccnu.edu.cn/ | 电话:027-67868680
-◆ 数学与统计学学院 | http://maths.ccnu.edu.cn/
-◆ 物理科学与技术学院 | http://phy.ccnu.edu.cn/ | 电话:027-67867017
-◆ 化学学院 | http://chem.ccnu.edu.cn/ | 电话:027-67867955
-◆ 生命科学学院 | http://bio.ccnu.edu.cn/ | 电话:+86-27-67867221
-◆ 计算机学院 | http://cs.ccnu.edu.cn/ | 邮箱:cs@ccnu.edu.cn | 电话:027-67868318
-◆ 城市与环境科学学院 | http://ccnucity.ccnu.edu.cn/ | 电话:027-67868305; 027-67861443; 027-67867610</t>
+    <t>心理学院 | http://psych.ccnu.edu.cn/ | 电话:027-67868680
+数学与统计学学院 | http://maths.ccnu.edu.cn/
+物理科学与技术学院 | http://phy.ccnu.edu.cn/ | 电话:027-67867017
+化学学院 | http://chem.ccnu.edu.cn/ | 电话:027-67867955
+生命科学学院 | http://bio.ccnu.edu.cn/ | 电话:+86-27-67867221
+计算机学院 | http://cs.ccnu.edu.cn/ | 邮箱:cs@ccnu.edu.cn | 电话:027-67868318
+城市与环境科学学院 | http://ccnucity.ccnu.edu.cn/ | 电话:027-67868305; 027-67861443; 027-67867610</t>
   </si>
   <si>
     <t>武汉理工大学</t>
@@ -4215,13 +4189,6 @@
   </si>
   <si>
     <t>地理科学学院 | http://dlkx.hunnu.edu.cn/ | 邮箱:zhxy@hunnu.edu.cn | 电话:0731-88872535
-国际汉语文化学院 | http://icclc.hunnu.edu.cn/ | 邮箱:icclc@hunnu.edu.cn | 电话:0731-88873017
-化学化工学院 | http://hgxy.hunnu.edu.cn/ | 电话:88872530
-生命科学学院 | http://lifescience.hunnu.edu.cn/ | 电话:18890054350); 0731-88872525
-数学与统计学院 | http://mc.hunnu.edu.cn/ | 电话:0731-88872515
-物理与电子科学学院 | http://wdy.hunnu.edu.cn | 邮箱:wdy@hunnu.edu.cn | 电话:0731-88872520
-信息科学与工程学院 | http://cise.hunnu.edu.cn | 邮箱:641381226@qq.com
-地理科学学院 | http://dlkx.hunnu.edu.cn/ | 邮箱:zhxy@hunnu.edu.cn | 电话:0731-88872535
 国际汉语文化学院 | http://icclc.hunnu.edu.cn/ | 邮箱:icclc@hunnu.edu.cn | 电话:0731-88873017
 化学化工学院 | http://hgxy.hunnu.edu.cn/ | 电话:88872530
 生命科学学院 | http://lifescience.hunnu.edu.cn/ | 电话:18890054350); 0731-88872525
@@ -6312,18 +6279,6 @@
 计算机与软件学院 | http://csse.szu.edu.cn/
 人工智能学院 | https://ai.szu.edu.cn/ | 电话:0755-26946884
 建筑与城市规划学院 | http://saup.szu.edu.cn/ | 电话:(0755)26732877; (0755)26536114
-土木与交通工程学院 | http://ce.szu.edu.cn/ | 电话:（0755）26735711
-心理学院 | http://psy.szu.edu.cn/ | 邮箱:psych@szu.edu.cn | 电话:075526917503
-数学科学学院 | http://math.szu.edu.cn/ | 电话:0755-26534791
-物理与光电工程学院 | http://cpoe.szu.edu.cn/ | 邮箱:cpoe@szu.edu.cn | 电话:0755-26538735
-化学与环境工程学院 | http://chem.szu.edu.cn/ | 电话:0755-26536141
-生命与海洋科学学院 | http://bio.szu.edu.cn/ | 邮箱:szsky@szu.edu.cn | 电话:0755-86713951
-机电与控制工程学院 | http://cmce.szu.edu.cn/ | 电话:0755-26536224
-材料学院 | http://cmse.szu.edu.cn/ | 邮箱:guoyanke@szu.edu.cn
-电子与信息工程学院 | http://ceie.szu.edu.cn/ | 邮箱:cie@szu.edu.cn | 电话:0755-26536198
-计算机与软件学院 | http://csse.szu.edu.cn/
-人工智能学院 | https://ai.szu.edu.cn/ | 电话:0755-26946884
-建筑与城市规划学院 | http://saup.szu.edu.cn/ | 电话:(0755)26732877; (0755)26536114
 土木与交通工程学院 | http://ce.szu.edu.cn/ | 电话:（0755）26735711</t>
   </si>
   <si>
@@ -6912,13 +6867,6 @@
 电气与电子工程学院 | http://eee.wzu.edu.cn/ | 邮箱:dqdzxy@wzu.edu.cn | 电话:0577-86689010
 计算机与人工智能学院 | http://ai.wzu.edu.cn/ | 邮箱:ai@wzu.edu.cn | 电话:0577-86599385; 0577-86590231; 0577-86599563
 建筑工程学院 | http://cace.wzu.edu.cn/ | 邮箱:wzjgxy@wzu.edu.cn | 电话:0577-86689611
-数理学院 | https://slxy.wzu.edu.cn/ | 邮箱:slxy@wzu.edu.cn | 电话:0577-86689098; 0577-86689528
-化学与材料工程学院 | https://chem.wzu.edu.cn/ | 邮箱:hxx@wzu.edu.cn | 电话:0577-86689360; 0577-86689300; 0577-86689302
-生命与环境科学学院 | https://shxy.wzu.edu.cn/
-机电工程学院 | https://jdxy.wzu.edu.cn/
-电气与电子工程学院 | https://eee.wzu.edu.cn/ | 邮箱:dqdzxy@wzu.edu.cn | 电话:0577-86689010
-计算机与人工智能学院 | https://ai.wzu.edu.cn/ | 邮箱:ai@wzu.edu.cn | 电话:0577-86599385; 0577-86590231; 0577-86599563
-建筑工程学院 | https://cace.wzu.edu.cn/ | 邮箱:wzjgxy@wzu.edu.cn | 电话:0577-86689611
 新材料与产业技术研究院 | https://inmit.wzu.edu.cn/ | 邮箱:wzumit@163.com | 电话:0577-85516217
 激光与光电智能制造研究院 | https://im.wzu.edu.cn | 邮箱:imlp@wzu.edu.cn | 电话:0577-85516755</t>
   </si>
@@ -7984,7 +7932,7 @@
         <v>26</v>
       </c>
       <c r="U4" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>45</v>
@@ -8694,7 +8642,7 @@
         <v>121</v>
       </c>
       <c r="U14" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>124</v>
@@ -10966,7 +10914,7 @@
         <v>26</v>
       </c>
       <c r="U46" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V46" s="4" t="s">
         <v>430</v>
@@ -11534,7 +11482,7 @@
         <v>26</v>
       </c>
       <c r="U54" s="4">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V54" s="4" t="s">
         <v>486</v>
@@ -12244,7 +12192,7 @@
         <v>26</v>
       </c>
       <c r="U64" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V64" s="4" t="s">
         <v>559</v>
@@ -14516,7 +14464,7 @@
         <v>26</v>
       </c>
       <c r="U96" s="4">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="V96" s="4" t="s">
         <v>817</v>
@@ -14942,7 +14890,7 @@
         <v>26</v>
       </c>
       <c r="U102" s="4">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="V102" s="4" t="s">
         <v>870</v>
@@ -19273,7 +19221,7 @@
         <v>1346</v>
       </c>
       <c r="U163" s="6">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="V163" s="6" t="s">
         <v>1347</v>
@@ -20480,7 +20428,7 @@
         <v>26</v>
       </c>
       <c r="U180" s="6">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V180" s="6" t="s">
         <v>1492</v>

--- a/dataset/全国重点院校/全国高校汇总表.xlsx
+++ b/dataset/全国重点院校/全国高校汇总表.xlsx
@@ -3930,14 +3930,14 @@
 生命健康学院 | http://slhs.hainanu.edu.cn | 邮箱:hdsmkx@hainanu.edu.cn | 电话:0898-66253203（
 机电工程学院 | http://smee.hainanu.edu.cn | 电话:0898-66267576; 0898-66271526; 0898-66267372
 材料科学与工程学院 | http://mse.hainanu.edu.cn | 邮箱:clxyzhb@hainanu.edu.cn | 电话:0898-66251982（
-电子科学与技术学院 | https://hd.hainanu.edu.cn/dzkx/
+电子科学与技术学院 | https://ee.hainanu.edu.cn
 信息与通信工程学院 | http://sice.hainanu.edu.cn | 邮箱:sice@hainan.edu.cn | 电话:0898-66279057
 计算机科学与技术学院 | http://cs.hainanu.edu.cn | 邮箱:cs@hainanu.edu.cn | 电话:0898-66278203
 网络空间安全学院 | https://scs.hainanu.edu.cn/ | 邮箱:scscs@hainanu.edu.cn | 电话:0898-66259127; 0898-66257132
 土木建筑工程学院 | http://scea.hainanu.edu.cn | 电话:0898-66279232
 海洋技术与装备学院 | http://smse.hainanu.edu.cn/ | 邮箱:sheny2000@hainanu.edu.cn; 991302@hainanu.edu.cn | 电话:0898-66192572; 0898-66255276
 环境科学与工程学院 | http://sese.hainanu.edu.cn | 电话:0898-66255157
-食品科学与工程学院 | https://hd.hainanu.edu.cn/shipin/
+食品科学与工程学院 | https://foodsci.hainanu.edu.cn | 邮箱:foodsci@hainanu.edu.cn; 992780@hainanu.edu.cn; 992415@hainanu.edu.cn | 电话:0898-66982750; 0898-66982801-; 0898-66192561（
 海洋生物与水产学院 | http://smbf.hainanu.edu.cn | 邮箱:xiesg@hainanu.edu.cn; 993928@hainanu.edu.cn; haiyyb@hainu.edu.cn | 电话:0898-66279184
 空天智能学院 | https://sai.hainanu.edu.cn/ | 邮箱:ktzn@hainanu.edu.cn | 电话:0898-66268297</t>
   </si>
@@ -4133,7 +4133,7 @@
 土木工程与建筑学院 | http://scea.whut.edu.cn/ | 电话:027-87651786
 资源与环境工程学院 | http://sree.whut.edu.cn/
 信息工程学院 | http://wutinfo.whut.edu.cn/
-人工智能学院 | http://csai.whut.edu.cn/
+人工智能学院 | https://ai.whut.edu.cn | 电话:027-87298226; 027-87566996; 027-87687326
 数学与统计学院 | http://maths.whut.edu.cn | 电话:027-87650137（
 物理与力学学院 | http://phymech.whut.edu.cn | 电话:027-87108026（
 化学化工学院 | http://cce.whut.edu.cn/ | 邮箱:hsxy@whut.edu.cn | 电话:027-87749379
@@ -4207,21 +4207,21 @@
     <t>做好处 处长</t>
   </si>
   <si>
-    <t>电气工程与自动化学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=dqxy&amp;type=w
-机械工程及自动化学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=jxxy&amp;type=w
-数学与统计学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=math&amp;type=w
-化工学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=che&amp;type=w
-土木工程学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=civil&amp;type=w
-环境与安全工程学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=es&amp;type=w
-生物科学与工程学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=bio&amp;type=w
-计算机与大数据学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=ccds&amp;type=w
-物理与信息工程学院、微电子学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=wx&amp;type=w
-化学学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=chem&amp;type=w
-建筑与城乡规划学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=jzxy&amp;type=w
-紫金地质与矿业学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=zjxy&amp;type=w
-材料科学与工程学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=cl&amp;type=w
-先进制造学院与海洋学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=xjzz&amp;type=w
-梅努斯国际工程学院 | https://www.fzu.edu.cn/system/resource/link.jsp?bmmc=miec&amp;type=w
+    <t>电气工程与自动化学院 | https://dqxy.fzu.edu.cn/ | 邮箱:dqxy@fzu.edu.cn; zhengx_1976@163.com; feixiongchen@fzu.edu.cn | 电话:0591-22866587; 0591-22866599; 0591-22866588
+机械工程及自动化学院 | https://jxxy.fzu.edu.cn/ | 邮箱:jxxyh@fzu.edu.cn; 819259992@qq.com; renzyrose@126.com | 电话:2024-04-10; 0591-22866262; 0591-22866170
+数学与统计学院 | https://math.fzu.edu.cn/ | 邮箱:yjliu@fzu.edu.cn; hcheng@fzu.edu.cn; jiangfei0591@163.com | 电话:0591-22860369; 0591-22860380; 0591-22860359
+化工学院 | https://che.fzu.edu.cn | 邮箱:syhg@fzu.edu.cn | 电话:0591-22865957; 0591-22865220; 0595-36218102
+土木工程学院 | https://civil.fzu.edu.cn | 电话:0591-22865351; 0591-22865373
+环境与安全工程学院 | https://es.fzu.edu.cn/ | 邮箱:liuwang@fzu.edu.cn; joexu@fzu.edu.cn; 439356896@qq.com | 电话:0591-22866099; 0591-22866356; 0591-22866069
+生物科学与工程学院 | https://bio.fzu.edu.cn | 电话:0591-22866276; 0591-22866277
+计算机与大数据学院 | https://ccds.fzu.edu.cn/ | 邮箱:mchen@fzu.edu.cn
+物理与信息工程学院、微电子学院 | https://wx.fzu.edu.cn | 邮箱:luxiaoqiang@fzu.edu.cn; wjm063@163.com; 1847735879@qq.com | 电话:0591-22865160; 0591-22865127; 0591-22865128
+化学学院 | https://chem.fzu.edu.cn | 邮箱:hxxy@fzu.edu.cn; 821494183@qq.com; zhongyuwu@fzu.edu.cn | 电话:0591-22866234; 0591-22866230; 0591-22866124
+建筑与城乡规划学院 | https://jzxy.fzu.edu.cn | 邮箱:jzxy@fzu.edu.cn | 电话:0591-22887607; 0591-22866383; 0591-22866386
+紫金地质与矿业学院 | https://zjxy.fzu.edu.cn | 邮箱:zjky@fzu.edu.cn | 电话:22865211; 0591-22865218; 0591-22865216
+材料科学与工程学院 | https://cl.fzu.edu.cn | 电话:0591-22866539
+先进制造学院与海洋学院 | https://xjzz.fzu.edu.cn/ | 电话:0595-82660803; 0595-82660810; 82660861（
+梅努斯国际工程学院 | https://miec.fzu.edu.cn | 邮箱:miec@fzu.edu.cn; miec_fzu@163.com; joseph.timoney@mu.ieDr | 电话:0591-22801600; 0591-22801601; 13665029308
 未来技术学院 | https://future.fzu.edu.cn/ | 邮箱:future@fzu.edu.cn | 电话:0591-22863835</t>
   </si>
   <si>
